--- a/xcheck/RESULTS-50.xlsx
+++ b/xcheck/RESULTS-50.xlsx
@@ -7,9 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50 apps (single)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="multi-app (concurrent)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity factors" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50 apps (single)" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="multi-app (concurrent)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,8 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -38,16 +40,16 @@
     </font>
     <font>
       <b val="1"/>
-      <i val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="001F3864"/>
     </font>
     <font>
       <i val="1"/>
       <color rgb="00808080"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
     </font>
   </fonts>
   <fills count="6">
@@ -69,12 +71,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,17 +92,22 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -467,6 +474,1493 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H55"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>app</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>QEMU insns</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>silicon insns</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>insn err %</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>QEMU GB/s</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>silicon GB/s</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>bandwidth err %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>elapsed s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>mem</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>536921108</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>547881096</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E2" s="5" t="n">
+        <v>4.931</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>2.531</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>mem-w</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>402703360</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>409609403</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>4.661</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>2.617</v>
+      </c>
+      <c r="G3" s="6" t="n">
+        <v>78.09999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.17</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>mm-big</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1364911785</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>1370228895</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.486</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.598</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>lz4</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>712769837</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>721442231</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-6.2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>sgm-a55-1t</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>23773139494</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>24142073329</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>-1.53</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="G6" t="n">
+        <v>116.8</v>
+      </c>
+      <c r="H6" t="n">
+        <v>17.63</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1079050055</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1082560905</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-36.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>sgm</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>10125614079</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>10155842310</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="G8" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4.56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>lz4-fast</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>281463026</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>304138792</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>-7.46</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="G9" t="n">
+        <v>33.9</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>rd-life</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>688350941</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>691991460</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G10" t="n">
+        <v>125.6</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.29</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>lua</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1065880704</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1073333237</v>
+      </c>
+      <c r="D11" s="4" t="n">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G11" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>cr-blowfish</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>308485272</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>309426132</v>
+      </c>
+      <c r="D12" s="4" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1452.2</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.13</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>sqlite</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>2574904942</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>2585886019</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G13" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.31</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>cr-rc4</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>377595401</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>383318247</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>-1.49</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-2.6</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>qoi</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>387938873</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>392304937</v>
+      </c>
+      <c r="D15" s="4" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="G15" t="n">
+        <v>167.1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>sqlite-heavy</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>5844762571</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>5871194558</v>
+      </c>
+      <c r="D16" s="4" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.03</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>bb-b64</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>728073329</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>832539047</v>
+      </c>
+      <c r="D17" s="8" t="n">
+        <v>-12.55</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-99.5</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>sha256-big</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1583178320</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>1588240243</v>
+      </c>
+      <c r="D18" s="4" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1531.4</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>bb-md5</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>421302488</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>440482683</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>-4.35</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-99.7</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>bzip2-fast</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>5475173421</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>5463900027</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-14.9</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>cr-b64</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>604031392</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>608918491</v>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>0.223</v>
+      </c>
+      <c r="G21" t="n">
+        <v>66</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>bb-sortn</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>16431116519</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>16783191876</v>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>-2.1</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G22" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H22" t="n">
+        <v>9.33</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>bzip2</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>8370753201</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>8388781131</v>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-32</v>
+      </c>
+      <c r="H23" t="n">
+        <v>6.07</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>bb-wc</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>557137503</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>567719116</v>
+      </c>
+      <c r="D24" s="4" t="n">
+        <v>-1.86</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-99.5</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>cr-aes</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>2371931130</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>2374887181</v>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1159.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>bb-gzip</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>3921678068</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>3940973082</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-99.09999999999999</v>
+      </c>
+      <c r="H26" t="n">
+        <v>2.41</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>bb-sed</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>1961929088</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>1989501558</v>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-98.3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.08</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>sort-big</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>3070649093</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>3077606417</v>
+      </c>
+      <c r="D28" s="4" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.118</v>
+      </c>
+      <c r="G28" t="n">
+        <v>244.7</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1.54</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>rd-plasma</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>3204908200</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>3209805063</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>0.022</v>
+      </c>
+      <c r="G29" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.18</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>8443316555</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>8452048813</v>
+      </c>
+      <c r="D30" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2038.7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>2.84</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>bb-awk</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>2589233094</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>2666087519</v>
+      </c>
+      <c r="D31" s="7" t="n">
+        <v>-2.88</v>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-98.3</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.56</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>bb-sha1</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1797037455</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1817646957</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-99.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.66</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>sort</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>1917050985</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>1925832657</v>
+      </c>
+      <c r="D33" s="4" t="n">
+        <v>-0.46</v>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="G33" t="n">
+        <v>265.2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>bb-gunzip</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>142006976</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>143307379</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>-0.91</v>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.2</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>rd-mandel</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>2433477828</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>2437786626</v>
+      </c>
+      <c r="D35" s="4" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="G35" t="n">
+        <v>60.6</v>
+      </c>
+      <c r="H35" t="n">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>bb-sha512</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1065952076</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>1086460745</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>-1.89</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-99.7</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>cr-md5</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>1546716576</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>1546841628</v>
+      </c>
+      <c r="D37" s="4" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="G37" t="n">
+        <v>1775.8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>bb-cksum</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>270634504</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>319977828</v>
+      </c>
+      <c r="D38" s="8" t="n">
+        <v>-15.42</v>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-99.59999999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.23</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>heatshrink</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>2747980761</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>2754157703</v>
+      </c>
+      <c r="D39" s="4" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="G39" t="n">
+        <v>63.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>cjson</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1494742289</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>1522807061</v>
+      </c>
+      <c r="D40" s="4" t="n">
+        <v>-1.84</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G40" t="n">
+        <v>26.2</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.28</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>pcg</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>1040050696</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1041115323</v>
+      </c>
+      <c r="D41" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-77.40000000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>pacman</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>25688907996</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>25714989204</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-89.59999999999999</v>
+      </c>
+      <c r="H42" t="n">
+        <v>14.26</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>parson</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1896753410</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>2001005821</v>
+      </c>
+      <c r="D43" s="7" t="n">
+        <v>-5.21</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="G43" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.84</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>bb-grep</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1268085715</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>1286057586</v>
+      </c>
+      <c r="D44" s="4" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-98.2</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>httpp</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1165593270</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1165848842</v>
+      </c>
+      <c r="D45" s="4" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-66.59999999999999</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>pacman-big</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>18907359660</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>18926519422</v>
+      </c>
+      <c r="D46" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-88.5</v>
+      </c>
+      <c r="H46" t="n">
+        <v>10.49</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>rd-ray</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>316170783</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>320310814</v>
+      </c>
+      <c r="D47" s="4" t="n">
+        <v>-1.29</v>
+      </c>
+      <c r="E47" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F47" s="5" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G47" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>tommath</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>497610617</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>500658352</v>
+      </c>
+      <c r="D48" s="4" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-5.4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>alu</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>1200049305</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1201018403</v>
+      </c>
+      <c r="D49" s="4" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-74.8</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>chase</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>214268019</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>203929213</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="E50" s="5" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="F50" s="5" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="G50" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>chase-big</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>316485763</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>328404010</v>
+      </c>
+      <c r="D51" s="7" t="n">
+        <v>-3.63</v>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="G51" t="n">
+        <v>6</v>
+      </c>
+      <c r="H51" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
+        <is>
+          <t>instructions: MAPE 1.75%, median 0.65%, 41 of 50 within 2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>bandwidth error is only meaningful for the 3 applications above 0.5 GB/s; below that the absolute traffic is too small for the ratio to mean anything</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>QEMU counts DERIVED from TCG plugins (linux-user); silicon counts MEASURED via ARM PMU (i.MX95, A55 core 0, pinned 1.8 GHz)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:O51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -582,7 +2076,7 @@
       <c r="E2" t="n">
         <v>788</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="11" t="n">
         <v>3.6</v>
       </c>
       <c r="G2" t="n">
@@ -591,7 +2085,7 @@
       <c r="H2" t="n">
         <v>979.2</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="11" t="n">
         <v>2.5</v>
       </c>
       <c r="J2" t="n">
@@ -600,7 +2094,7 @@
       <c r="K2" t="n">
         <v>1767.2</v>
       </c>
-      <c r="L2" s="3" t="n">
+      <c r="L2" s="11" t="n">
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
@@ -633,7 +2127,7 @@
       <c r="E3" t="n">
         <v>804.8</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="11" t="n">
         <v>1.3</v>
       </c>
       <c r="G3" t="n">
@@ -642,7 +2136,7 @@
       <c r="H3" t="n">
         <v>990.6</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="I3" s="11" t="n">
         <v>4.2</v>
       </c>
       <c r="J3" t="n">
@@ -651,7 +2145,7 @@
       <c r="K3" t="n">
         <v>1795.3</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="11" t="n">
         <v>2.9</v>
       </c>
       <c r="M3" t="n">
@@ -684,7 +2178,7 @@
       <c r="E4" t="n">
         <v>626.5</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="G4" t="n">
@@ -693,7 +2187,7 @@
       <c r="H4" t="n">
         <v>931.1</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="I4" s="11" t="n">
         <v>5.1</v>
       </c>
       <c r="J4" t="n">
@@ -702,7 +2196,7 @@
       <c r="K4" t="n">
         <v>1557.6</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="11" t="n">
         <v>7</v>
       </c>
       <c r="M4" t="n">
@@ -735,7 +2229,7 @@
       <c r="E5" t="n">
         <v>631.9</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>22.8</v>
       </c>
       <c r="G5" t="n">
@@ -744,7 +2238,7 @@
       <c r="H5" t="n">
         <v>897.1</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="I5" s="11" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
@@ -753,7 +2247,7 @@
       <c r="K5" t="n">
         <v>1529</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" s="6" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" t="n">
@@ -786,7 +2280,7 @@
       <c r="E6" t="n">
         <v>597</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
@@ -795,7 +2289,7 @@
       <c r="H6" t="n">
         <v>915</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="I6" s="11" t="n">
         <v>5.8</v>
       </c>
       <c r="J6" t="n">
@@ -804,7 +2298,7 @@
       <c r="K6" t="n">
         <v>1512</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="12" t="n">
         <v>10.2</v>
       </c>
       <c r="M6" t="n">
@@ -837,7 +2331,7 @@
       <c r="E7" t="n">
         <v>609.8</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>19.9</v>
       </c>
       <c r="G7" t="n">
@@ -846,7 +2340,7 @@
       <c r="H7" t="n">
         <v>904.9</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="I7" s="11" t="n">
         <v>5.3</v>
       </c>
       <c r="J7" t="n">
@@ -855,7 +2349,7 @@
       <c r="K7" t="n">
         <v>1514.7</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="12" t="n">
         <v>11.2</v>
       </c>
       <c r="M7" t="n">
@@ -888,7 +2382,7 @@
       <c r="E8" t="n">
         <v>691.2</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>25.2</v>
       </c>
       <c r="G8" t="n">
@@ -897,7 +2391,7 @@
       <c r="H8" t="n">
         <v>922.9</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="I8" s="11" t="n">
         <v>7.1</v>
       </c>
       <c r="J8" t="n">
@@ -906,7 +2400,7 @@
       <c r="K8" t="n">
         <v>1614.2</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L8" s="6" t="n">
         <v>14.8</v>
       </c>
       <c r="M8" t="n">
@@ -939,7 +2433,7 @@
       <c r="E9" t="n">
         <v>647.1</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>23.1</v>
       </c>
       <c r="G9" t="n">
@@ -948,7 +2442,7 @@
       <c r="H9" t="n">
         <v>917.5</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="I9" s="11" t="n">
         <v>6.1</v>
       </c>
       <c r="J9" t="n">
@@ -957,7 +2451,7 @@
       <c r="K9" t="n">
         <v>1564.6</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" s="6" t="n">
         <v>13.1</v>
       </c>
       <c r="M9" t="n">
@@ -990,7 +2484,7 @@
       <c r="E10" t="n">
         <v>601.8</v>
       </c>
-      <c r="F10" s="3" t="n">
+      <c r="F10" s="11" t="n">
         <v>7.6</v>
       </c>
       <c r="G10" t="n">
@@ -999,7 +2493,7 @@
       <c r="H10" t="n">
         <v>922.8</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="I10" s="11" t="n">
         <v>5.9</v>
       </c>
       <c r="J10" t="n">
@@ -1008,7 +2502,7 @@
       <c r="K10" t="n">
         <v>1524.6</v>
       </c>
-      <c r="L10" s="3" t="n">
+      <c r="L10" s="11" t="n">
         <v>6.6</v>
       </c>
       <c r="M10" t="n">
@@ -1041,7 +2535,7 @@
       <c r="E11" t="n">
         <v>585.9</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="6" t="n">
         <v>13.4</v>
       </c>
       <c r="G11" t="n">
@@ -1050,7 +2544,7 @@
       <c r="H11" t="n">
         <v>871</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="I11" s="11" t="n">
         <v>1.8</v>
       </c>
       <c r="J11" t="n">
@@ -1059,7 +2553,7 @@
       <c r="K11" t="n">
         <v>1456.9</v>
       </c>
-      <c r="L11" s="3" t="n">
+      <c r="L11" s="11" t="n">
         <v>6.5</v>
       </c>
       <c r="M11" t="n">
@@ -1092,7 +2586,7 @@
       <c r="E12" t="n">
         <v>609.4</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="6" t="n">
         <v>14.9</v>
       </c>
       <c r="G12" t="n">
@@ -1101,7 +2595,7 @@
       <c r="H12" t="n">
         <v>907.5</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="I12" s="11" t="n">
         <v>5.7</v>
       </c>
       <c r="J12" t="n">
@@ -1110,7 +2604,7 @@
       <c r="K12" t="n">
         <v>1516.9</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="12" t="n">
         <v>9.4</v>
       </c>
       <c r="M12" t="n">
@@ -1143,7 +2637,7 @@
       <c r="E13" t="n">
         <v>580.4</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="6" t="n">
         <v>14.4</v>
       </c>
       <c r="G13" t="n">
@@ -1152,7 +2646,7 @@
       <c r="H13" t="n">
         <v>851.5</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="I13" s="11" t="n">
         <v>0.3</v>
       </c>
       <c r="J13" t="n">
@@ -1161,7 +2655,7 @@
       <c r="K13" t="n">
         <v>1431.9</v>
       </c>
-      <c r="L13" s="3" t="n">
+      <c r="L13" s="11" t="n">
         <v>5.6</v>
       </c>
       <c r="M13" t="n">
@@ -1194,7 +2688,7 @@
       <c r="E14" t="n">
         <v>569.1</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="6" t="n">
         <v>15.5</v>
       </c>
       <c r="G14" t="n">
@@ -1203,7 +2697,7 @@
       <c r="H14" t="n">
         <v>908.2</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="I14" s="11" t="n">
         <v>5.8</v>
       </c>
       <c r="J14" t="n">
@@ -1212,7 +2706,7 @@
       <c r="K14" t="n">
         <v>1477.3</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="12" t="n">
         <v>9.6</v>
       </c>
       <c r="M14" t="n">
@@ -1245,7 +2739,7 @@
       <c r="E15" t="n">
         <v>612.9</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="6" t="n">
         <v>12.4</v>
       </c>
       <c r="G15" t="n">
@@ -1254,7 +2748,7 @@
       <c r="H15" t="n">
         <v>911.4</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="I15" s="11" t="n">
         <v>5.7</v>
       </c>
       <c r="J15" t="n">
@@ -1263,7 +2757,7 @@
       <c r="K15" t="n">
         <v>1524.3</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="12" t="n">
         <v>8.4</v>
       </c>
       <c r="M15" t="n">
@@ -1296,7 +2790,7 @@
       <c r="E16" t="n">
         <v>575.6</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="6" t="n">
         <v>13.9</v>
       </c>
       <c r="G16" t="n">
@@ -1305,7 +2799,7 @@
       <c r="H16" t="n">
         <v>858</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="I16" s="11" t="n">
         <v>0.4</v>
       </c>
       <c r="J16" t="n">
@@ -1314,7 +2808,7 @@
       <c r="K16" t="n">
         <v>1433.6</v>
       </c>
-      <c r="L16" s="3" t="n">
+      <c r="L16" s="11" t="n">
         <v>5.8</v>
       </c>
       <c r="M16" t="n">
@@ -1347,7 +2841,7 @@
       <c r="E17" t="n">
         <v>572.9</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="6" t="n">
         <v>15.9</v>
       </c>
       <c r="G17" t="n">
@@ -1356,7 +2850,7 @@
       <c r="H17" t="n">
         <v>902.7</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="I17" s="11" t="n">
         <v>5.5</v>
       </c>
       <c r="J17" t="n">
@@ -1365,7 +2859,7 @@
       <c r="K17" t="n">
         <v>1475.6</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="12" t="n">
         <v>9.5</v>
       </c>
       <c r="M17" t="n">
@@ -1398,7 +2892,7 @@
       <c r="E18" t="n">
         <v>572.6</v>
       </c>
-      <c r="F18" s="3" t="n">
+      <c r="F18" s="11" t="n">
         <v>5.6</v>
       </c>
       <c r="G18" t="n">
@@ -1407,7 +2901,7 @@
       <c r="H18" t="n">
         <v>903.4</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="I18" s="11" t="n">
         <v>5.2</v>
       </c>
       <c r="J18" t="n">
@@ -1416,7 +2910,7 @@
       <c r="K18" t="n">
         <v>1476</v>
       </c>
-      <c r="L18" s="3" t="n">
+      <c r="L18" s="11" t="n">
         <v>5.4</v>
       </c>
       <c r="M18" t="n">
@@ -1449,7 +2943,7 @@
       <c r="E19" t="n">
         <v>578.6</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="6" t="n">
         <v>12.9</v>
       </c>
       <c r="G19" t="n">
@@ -1458,7 +2952,7 @@
       <c r="H19" t="n">
         <v>905</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="I19" s="11" t="n">
         <v>5.6</v>
       </c>
       <c r="J19" t="n">
@@ -1467,7 +2961,7 @@
       <c r="K19" t="n">
         <v>1483.6</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="12" t="n">
         <v>8.5</v>
       </c>
       <c r="M19" t="n">
@@ -1500,7 +2994,7 @@
       <c r="E20" t="n">
         <v>574.3</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="6" t="n">
         <v>13.9</v>
       </c>
       <c r="G20" t="n">
@@ -1509,7 +3003,7 @@
       <c r="H20" t="n">
         <v>894.8</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="I20" s="11" t="n">
         <v>4.5</v>
       </c>
       <c r="J20" t="n">
@@ -1518,7 +3012,7 @@
       <c r="K20" t="n">
         <v>1469.1</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M20" t="n">
@@ -1551,7 +3045,7 @@
       <c r="E21" t="n">
         <v>587.1</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="6" t="n">
         <v>12.1</v>
       </c>
       <c r="G21" t="n">
@@ -1560,7 +3054,7 @@
       <c r="H21" t="n">
         <v>919.2</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="I21" s="11" t="n">
         <v>6.3</v>
       </c>
       <c r="J21" t="n">
@@ -1569,7 +3063,7 @@
       <c r="K21" t="n">
         <v>1506.4</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="12" t="n">
         <v>8.6</v>
       </c>
       <c r="M21" t="n">
@@ -1602,7 +3096,7 @@
       <c r="E22" t="n">
         <v>549</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="12" t="n">
         <v>10.7</v>
       </c>
       <c r="G22" t="n">
@@ -1611,7 +3105,7 @@
       <c r="H22" t="n">
         <v>888.7</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="I22" s="11" t="n">
         <v>3.8</v>
       </c>
       <c r="J22" t="n">
@@ -1620,7 +3114,7 @@
       <c r="K22" t="n">
         <v>1437.7</v>
       </c>
-      <c r="L22" s="3" t="n">
+      <c r="L22" s="11" t="n">
         <v>6.4</v>
       </c>
       <c r="M22" t="n">
@@ -1653,7 +3147,7 @@
       <c r="E23" t="n">
         <v>537.9</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="12" t="n">
         <v>10.6</v>
       </c>
       <c r="G23" t="n">
@@ -1662,7 +3156,7 @@
       <c r="H23" t="n">
         <v>906.5</v>
       </c>
-      <c r="I23" s="3" t="n">
+      <c r="I23" s="11" t="n">
         <v>5.5</v>
       </c>
       <c r="J23" t="n">
@@ -1671,7 +3165,7 @@
       <c r="K23" t="n">
         <v>1444.4</v>
       </c>
-      <c r="L23" s="3" t="n">
+      <c r="L23" s="11" t="n">
         <v>7.4</v>
       </c>
       <c r="M23" t="n">
@@ -1704,7 +3198,7 @@
       <c r="E24" t="n">
         <v>570.5</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="12" t="n">
         <v>9.4</v>
       </c>
       <c r="G24" t="n">
@@ -1713,7 +3207,7 @@
       <c r="H24" t="n">
         <v>896.8</v>
       </c>
-      <c r="I24" s="3" t="n">
+      <c r="I24" s="11" t="n">
         <v>4.7</v>
       </c>
       <c r="J24" t="n">
@@ -1722,7 +3216,7 @@
       <c r="K24" t="n">
         <v>1467.4</v>
       </c>
-      <c r="L24" s="3" t="n">
+      <c r="L24" s="11" t="n">
         <v>6.5</v>
       </c>
       <c r="M24" t="n">
@@ -1755,7 +3249,7 @@
       <c r="E25" t="n">
         <v>544.5</v>
       </c>
-      <c r="F25" s="3" t="n">
+      <c r="F25" s="11" t="n">
         <v>3.9</v>
       </c>
       <c r="G25" t="n">
@@ -1764,7 +3258,7 @@
       <c r="H25" t="n">
         <v>900.7</v>
       </c>
-      <c r="I25" s="3" t="n">
+      <c r="I25" s="11" t="n">
         <v>5.1</v>
       </c>
       <c r="J25" t="n">
@@ -1773,7 +3267,7 @@
       <c r="K25" t="n">
         <v>1445.3</v>
       </c>
-      <c r="L25" s="3" t="n">
+      <c r="L25" s="11" t="n">
         <v>4.6</v>
       </c>
       <c r="M25" t="n">
@@ -1806,7 +3300,7 @@
       <c r="E26" t="n">
         <v>566.6</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="6" t="n">
         <v>14.9</v>
       </c>
       <c r="G26" t="n">
@@ -1815,7 +3309,7 @@
       <c r="H26" t="n">
         <v>866.3</v>
       </c>
-      <c r="I26" s="3" t="n">
+      <c r="I26" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="J26" t="n">
@@ -1824,7 +3318,7 @@
       <c r="K26" t="n">
         <v>1433</v>
       </c>
-      <c r="L26" s="3" t="n">
+      <c r="L26" s="11" t="n">
         <v>6.8</v>
       </c>
       <c r="M26" t="n">
@@ -1857,7 +3351,7 @@
       <c r="E27" t="n">
         <v>563</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="6" t="n">
         <v>13</v>
       </c>
       <c r="G27" t="n">
@@ -1866,7 +3360,7 @@
       <c r="H27" t="n">
         <v>862</v>
       </c>
-      <c r="I27" s="3" t="n">
+      <c r="I27" s="11" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
@@ -1875,7 +3369,7 @@
       <c r="K27" t="n">
         <v>1425</v>
       </c>
-      <c r="L27" s="3" t="n">
+      <c r="L27" s="11" t="n">
         <v>5.7</v>
       </c>
       <c r="M27" t="n">
@@ -1908,7 +3402,7 @@
       <c r="E28" t="n">
         <v>574.1</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="12" t="n">
         <v>9.1</v>
       </c>
       <c r="G28" t="n">
@@ -1917,7 +3411,7 @@
       <c r="H28" t="n">
         <v>908.2</v>
       </c>
-      <c r="I28" s="3" t="n">
+      <c r="I28" s="11" t="n">
         <v>5.1</v>
       </c>
       <c r="J28" t="n">
@@ -1926,7 +3420,7 @@
       <c r="K28" t="n">
         <v>1482.3</v>
       </c>
-      <c r="L28" s="3" t="n">
+      <c r="L28" s="11" t="n">
         <v>6.6</v>
       </c>
       <c r="M28" t="n">
@@ -1959,7 +3453,7 @@
       <c r="E29" t="n">
         <v>532</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="12" t="n">
         <v>10.3</v>
       </c>
       <c r="G29" t="n">
@@ -1968,7 +3462,7 @@
       <c r="H29" t="n">
         <v>902.4</v>
       </c>
-      <c r="I29" s="3" t="n">
+      <c r="I29" s="11" t="n">
         <v>5.4</v>
       </c>
       <c r="J29" t="n">
@@ -1977,7 +3471,7 @@
       <c r="K29" t="n">
         <v>1434.4</v>
       </c>
-      <c r="L29" s="3" t="n">
+      <c r="L29" s="11" t="n">
         <v>7.2</v>
       </c>
       <c r="M29" t="n">
@@ -2010,7 +3504,7 @@
       <c r="E30" t="n">
         <v>556.2</v>
       </c>
-      <c r="F30" s="3" t="n">
+      <c r="F30" s="11" t="n">
         <v>2.6</v>
       </c>
       <c r="G30" t="n">
@@ -2019,7 +3513,7 @@
       <c r="H30" t="n">
         <v>901.6</v>
       </c>
-      <c r="I30" s="3" t="n">
+      <c r="I30" s="11" t="n">
         <v>5</v>
       </c>
       <c r="J30" t="n">
@@ -2028,7 +3522,7 @@
       <c r="K30" t="n">
         <v>1457.8</v>
       </c>
-      <c r="L30" s="3" t="n">
+      <c r="L30" s="11" t="n">
         <v>4.1</v>
       </c>
       <c r="M30" t="n">
@@ -2061,7 +3555,7 @@
       <c r="E31" t="n">
         <v>561.3</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="6" t="n">
         <v>13.9</v>
       </c>
       <c r="G31" t="n">
@@ -2070,7 +3564,7 @@
       <c r="H31" t="n">
         <v>866.8</v>
       </c>
-      <c r="I31" s="3" t="n">
+      <c r="I31" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="J31" t="n">
@@ -2079,7 +3573,7 @@
       <c r="K31" t="n">
         <v>1428.1</v>
       </c>
-      <c r="L31" s="3" t="n">
+      <c r="L31" s="11" t="n">
         <v>6.4</v>
       </c>
       <c r="M31" t="n">
@@ -2112,7 +3606,7 @@
       <c r="E32" t="n">
         <v>545.9</v>
       </c>
-      <c r="F32" s="3" t="n">
+      <c r="F32" s="11" t="n">
         <v>3.2</v>
       </c>
       <c r="G32" t="n">
@@ -2121,7 +3615,7 @@
       <c r="H32" t="n">
         <v>875.3</v>
       </c>
-      <c r="I32" s="3" t="n">
+      <c r="I32" s="11" t="n">
         <v>2.3</v>
       </c>
       <c r="J32" t="n">
@@ -2130,7 +3624,7 @@
       <c r="K32" t="n">
         <v>1421.2</v>
       </c>
-      <c r="L32" s="3" t="n">
+      <c r="L32" s="11" t="n">
         <v>2.7</v>
       </c>
       <c r="M32" t="n">
@@ -2163,7 +3657,7 @@
       <c r="E33" t="n">
         <v>570.3</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="12" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G33" t="n">
@@ -2172,7 +3666,7 @@
       <c r="H33" t="n">
         <v>902.8</v>
       </c>
-      <c r="I33" s="3" t="n">
+      <c r="I33" s="11" t="n">
         <v>4.7</v>
       </c>
       <c r="J33" t="n">
@@ -2181,7 +3675,7 @@
       <c r="K33" t="n">
         <v>1473</v>
       </c>
-      <c r="L33" s="3" t="n">
+      <c r="L33" s="11" t="n">
         <v>6.5</v>
       </c>
       <c r="M33" t="n">
@@ -2214,7 +3708,7 @@
       <c r="E34" t="n">
         <v>603.1</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="6" t="n">
         <v>19.1</v>
       </c>
       <c r="G34" t="n">
@@ -2223,7 +3717,7 @@
       <c r="H34" t="n">
         <v>875.3</v>
       </c>
-      <c r="I34" s="3" t="n">
+      <c r="I34" s="11" t="n">
         <v>2.5</v>
       </c>
       <c r="J34" t="n">
@@ -2232,7 +3726,7 @@
       <c r="K34" t="n">
         <v>1478.4</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="12" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M34" t="n">
@@ -2265,7 +3759,7 @@
       <c r="E35" t="n">
         <v>520.3</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="12" t="n">
         <v>10.8</v>
       </c>
       <c r="G35" t="n">
@@ -2274,7 +3768,7 @@
       <c r="H35" t="n">
         <v>897.6</v>
       </c>
-      <c r="I35" s="3" t="n">
+      <c r="I35" s="11" t="n">
         <v>5</v>
       </c>
       <c r="J35" t="n">
@@ -2283,7 +3777,7 @@
       <c r="K35" t="n">
         <v>1417.9</v>
       </c>
-      <c r="L35" s="3" t="n">
+      <c r="L35" s="11" t="n">
         <v>7.1</v>
       </c>
       <c r="M35" t="n">
@@ -2316,7 +3810,7 @@
       <c r="E36" t="n">
         <v>570</v>
       </c>
-      <c r="F36" s="3" t="n">
+      <c r="F36" s="11" t="n">
         <v>7.8</v>
       </c>
       <c r="G36" t="n">
@@ -2325,7 +3819,7 @@
       <c r="H36" t="n">
         <v>899.6</v>
       </c>
-      <c r="I36" s="3" t="n">
+      <c r="I36" s="11" t="n">
         <v>5</v>
       </c>
       <c r="J36" t="n">
@@ -2334,7 +3828,7 @@
       <c r="K36" t="n">
         <v>1469.6</v>
       </c>
-      <c r="L36" s="3" t="n">
+      <c r="L36" s="11" t="n">
         <v>6.1</v>
       </c>
       <c r="M36" t="n">
@@ -2367,7 +3861,7 @@
       <c r="E37" t="n">
         <v>572.3</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="12" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="G37" t="n">
@@ -2376,7 +3870,7 @@
       <c r="H37" t="n">
         <v>905.5</v>
       </c>
-      <c r="I37" s="3" t="n">
+      <c r="I37" s="11" t="n">
         <v>5.4</v>
       </c>
       <c r="J37" t="n">
@@ -2385,7 +3879,7 @@
       <c r="K37" t="n">
         <v>1477.8</v>
       </c>
-      <c r="L37" s="3" t="n">
+      <c r="L37" s="11" t="n">
         <v>6.7</v>
       </c>
       <c r="M37" t="n">
@@ -2418,7 +3912,7 @@
       <c r="E38" t="n">
         <v>534.5</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="6" t="n">
         <v>13.2</v>
       </c>
       <c r="G38" t="n">
@@ -2427,7 +3921,7 @@
       <c r="H38" t="n">
         <v>902.9</v>
       </c>
-      <c r="I38" s="3" t="n">
+      <c r="I38" s="11" t="n">
         <v>5.6</v>
       </c>
       <c r="J38" t="n">
@@ -2436,7 +3930,7 @@
       <c r="K38" t="n">
         <v>1437.4</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="L38" s="12" t="n">
         <v>8.4</v>
       </c>
       <c r="M38" t="n">
@@ -2469,7 +3963,7 @@
       <c r="E39" t="n">
         <v>541.6</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="G39" t="n">
@@ -2478,7 +3972,7 @@
       <c r="H39" t="n">
         <v>898.1</v>
       </c>
-      <c r="I39" s="3" t="n">
+      <c r="I39" s="11" t="n">
         <v>4.9</v>
       </c>
       <c r="J39" t="n">
@@ -2487,7 +3981,7 @@
       <c r="K39" t="n">
         <v>1439.7</v>
       </c>
-      <c r="L39" s="3" t="n">
+      <c r="L39" s="11" t="n">
         <v>6.5</v>
       </c>
       <c r="M39" t="n">
@@ -2520,7 +4014,7 @@
       <c r="E40" t="n">
         <v>509.7</v>
       </c>
-      <c r="F40" s="3" t="n">
+      <c r="F40" s="11" t="n">
         <v>5.8</v>
       </c>
       <c r="G40" t="n">
@@ -2529,7 +4023,7 @@
       <c r="H40" t="n">
         <v>910.3</v>
       </c>
-      <c r="I40" s="3" t="n">
+      <c r="I40" s="11" t="n">
         <v>5.7</v>
       </c>
       <c r="J40" t="n">
@@ -2538,7 +4032,7 @@
       <c r="K40" t="n">
         <v>1420.1</v>
       </c>
-      <c r="L40" s="3" t="n">
+      <c r="L40" s="11" t="n">
         <v>5.7</v>
       </c>
       <c r="M40" t="n">
@@ -2571,7 +4065,7 @@
       <c r="E41" t="n">
         <v>579.5</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="6" t="n">
         <v>14.6</v>
       </c>
       <c r="G41" t="n">
@@ -2580,7 +4074,7 @@
       <c r="H41" t="n">
         <v>839.2</v>
       </c>
-      <c r="I41" s="3" t="n">
+      <c r="I41" s="11" t="n">
         <v>1.7</v>
       </c>
       <c r="J41" t="n">
@@ -2589,7 +4083,7 @@
       <c r="K41" t="n">
         <v>1418.6</v>
       </c>
-      <c r="L41" s="3" t="n">
+      <c r="L41" s="11" t="n">
         <v>4.9</v>
       </c>
       <c r="M41" t="n">
@@ -2622,7 +4116,7 @@
       <c r="E42" t="n">
         <v>540.1</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="12" t="n">
         <v>9.4</v>
       </c>
       <c r="G42" t="n">
@@ -2631,7 +4125,7 @@
       <c r="H42" t="n">
         <v>845.7</v>
       </c>
-      <c r="I42" s="3" t="n">
+      <c r="I42" s="11" t="n">
         <v>0.9</v>
       </c>
       <c r="J42" t="n">
@@ -2640,7 +4134,7 @@
       <c r="K42" t="n">
         <v>1385.9</v>
       </c>
-      <c r="L42" s="3" t="n">
+      <c r="L42" s="11" t="n">
         <v>3.1</v>
       </c>
       <c r="M42" t="n">
@@ -2673,7 +4167,7 @@
       <c r="E43" t="n">
         <v>518.2</v>
       </c>
-      <c r="F43" s="3" t="n">
+      <c r="F43" s="11" t="n">
         <v>7.6</v>
       </c>
       <c r="G43" t="n">
@@ -2682,7 +4176,7 @@
       <c r="H43" t="n">
         <v>913.3</v>
       </c>
-      <c r="I43" s="3" t="n">
+      <c r="I43" s="11" t="n">
         <v>5.8</v>
       </c>
       <c r="J43" t="n">
@@ -2691,7 +4185,7 @@
       <c r="K43" t="n">
         <v>1431.5</v>
       </c>
-      <c r="L43" s="3" t="n">
+      <c r="L43" s="11" t="n">
         <v>6.5</v>
       </c>
       <c r="M43" t="n">
@@ -2724,7 +4218,7 @@
       <c r="E44" t="n">
         <v>546</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="12" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="G44" t="n">
@@ -2733,7 +4227,7 @@
       <c r="H44" t="n">
         <v>859.5</v>
       </c>
-      <c r="I44" s="3" t="n">
+      <c r="I44" s="11" t="n">
         <v>0.7</v>
       </c>
       <c r="J44" t="n">
@@ -2742,7 +4236,7 @@
       <c r="K44" t="n">
         <v>1405.6</v>
       </c>
-      <c r="L44" s="3" t="n">
+      <c r="L44" s="11" t="n">
         <v>4.2</v>
       </c>
       <c r="M44" t="n">
@@ -2775,7 +4269,7 @@
       <c r="E45" t="n">
         <v>550.6</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="12" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="G45" t="n">
@@ -2784,7 +4278,7 @@
       <c r="H45" t="n">
         <v>840.5</v>
       </c>
-      <c r="I45" s="3" t="n">
+      <c r="I45" s="11" t="n">
         <v>1.6</v>
       </c>
       <c r="J45" t="n">
@@ -2793,7 +4287,7 @@
       <c r="K45" t="n">
         <v>1391.1</v>
       </c>
-      <c r="L45" s="3" t="n">
+      <c r="L45" s="11" t="n">
         <v>2.3</v>
       </c>
       <c r="M45" t="n">
@@ -2826,7 +4320,7 @@
       <c r="E46" t="n">
         <v>539</v>
       </c>
-      <c r="F46" s="4" t="n">
+      <c r="F46" s="12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="G46" t="n">
@@ -2835,7 +4329,7 @@
       <c r="H46" t="n">
         <v>842.7</v>
       </c>
-      <c r="I46" s="3" t="n">
+      <c r="I46" s="11" t="n">
         <v>1.3</v>
       </c>
       <c r="J46" t="n">
@@ -2844,7 +4338,7 @@
       <c r="K46" t="n">
         <v>1381.7</v>
       </c>
-      <c r="L46" s="3" t="n">
+      <c r="L46" s="11" t="n">
         <v>2.8</v>
       </c>
       <c r="M46" t="n">
@@ -2877,7 +4371,7 @@
       <c r="E47" t="n">
         <v>464.7</v>
       </c>
-      <c r="F47" s="3" t="n">
+      <c r="F47" s="11" t="n">
         <v>6.1</v>
       </c>
       <c r="G47" t="n">
@@ -2886,7 +4380,7 @@
       <c r="H47" t="n">
         <v>902.8</v>
       </c>
-      <c r="I47" s="3" t="n">
+      <c r="I47" s="11" t="n">
         <v>5.5</v>
       </c>
       <c r="J47" t="n">
@@ -2895,7 +4389,7 @@
       <c r="K47" t="n">
         <v>1367.4</v>
       </c>
-      <c r="L47" s="3" t="n">
+      <c r="L47" s="11" t="n">
         <v>5.7</v>
       </c>
       <c r="M47" t="n">
@@ -2928,7 +4422,7 @@
       <c r="E48" t="n">
         <v>532</v>
       </c>
-      <c r="F48" s="4" t="n">
+      <c r="F48" s="12" t="n">
         <v>11.4</v>
       </c>
       <c r="G48" t="n">
@@ -2937,7 +4431,7 @@
       <c r="H48" t="n">
         <v>840.4</v>
       </c>
-      <c r="I48" s="3" t="n">
+      <c r="I48" s="11" t="n">
         <v>1.5</v>
       </c>
       <c r="J48" t="n">
@@ -2946,7 +4440,7 @@
       <c r="K48" t="n">
         <v>1372.4</v>
       </c>
-      <c r="L48" s="3" t="n">
+      <c r="L48" s="11" t="n">
         <v>3.5</v>
       </c>
       <c r="M48" t="n">
@@ -2979,7 +4473,7 @@
       <c r="E49" t="n">
         <v>523.9</v>
       </c>
-      <c r="F49" s="3" t="n">
+      <c r="F49" s="11" t="n">
         <v>6.7</v>
       </c>
       <c r="G49" t="n">
@@ -2988,7 +4482,7 @@
       <c r="H49" t="n">
         <v>830.8</v>
       </c>
-      <c r="I49" s="3" t="n">
+      <c r="I49" s="11" t="n">
         <v>2.7</v>
       </c>
       <c r="J49" t="n">
@@ -2997,7 +4491,7 @@
       <c r="K49" t="n">
         <v>1354.7</v>
       </c>
-      <c r="L49" s="3" t="n">
+      <c r="L49" s="11" t="n">
         <v>0.9</v>
       </c>
       <c r="M49" t="n">
@@ -3030,7 +4524,7 @@
       <c r="E50" t="n">
         <v>385.6</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="6" t="n">
         <v>15</v>
       </c>
       <c r="G50" t="n">
@@ -3039,7 +4533,7 @@
       <c r="H50" t="n">
         <v>909.2</v>
       </c>
-      <c r="I50" s="3" t="n">
+      <c r="I50" s="11" t="n">
         <v>5.4</v>
       </c>
       <c r="J50" t="n">
@@ -3048,7 +4542,7 @@
       <c r="K50" t="n">
         <v>1294.9</v>
       </c>
-      <c r="L50" s="3" t="n">
+      <c r="L50" s="11" t="n">
         <v>0.7</v>
       </c>
       <c r="M50" t="n">
@@ -3081,7 +4575,7 @@
       <c r="E51" t="n">
         <v>396.3</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="6" t="n">
         <v>12.4</v>
       </c>
       <c r="G51" t="n">
@@ -3090,7 +4584,7 @@
       <c r="H51" t="n">
         <v>917.3</v>
       </c>
-      <c r="I51" s="3" t="n">
+      <c r="I51" s="11" t="n">
         <v>6.1</v>
       </c>
       <c r="J51" t="n">
@@ -3099,7 +4593,7 @@
       <c r="K51" t="n">
         <v>1313.6</v>
       </c>
-      <c r="L51" s="3" t="n">
+      <c r="L51" s="11" t="n">
         <v>0.6</v>
       </c>
       <c r="M51" t="n">
@@ -3119,7 +4613,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3211,7 +4705,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
         <is>
           <t>REALISTIC EDGE WORKLOADS</t>
         </is>
@@ -3255,10 +4749,10 @@
       <c r="K3" t="n">
         <v>1704</v>
       </c>
-      <c r="L3" s="3" t="n">
+      <c r="L3" s="11" t="n">
         <v>5.8</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="M3" s="11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3300,10 +4794,10 @@
       <c r="K4" t="n">
         <v>2189</v>
       </c>
-      <c r="L4" s="3" t="n">
+      <c r="L4" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="3" t="n">
+      <c r="M4" s="11" t="n">
         <v>3.1</v>
       </c>
     </row>
@@ -3345,15 +4839,15 @@
       <c r="K5" t="n">
         <v>2561</v>
       </c>
-      <c r="L5" s="3" t="n">
+      <c r="L5" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="3" t="n">
+      <c r="M5" s="11" t="n">
         <v>0.7</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>CONTROLS - synthetic / benchmark mixes</t>
         </is>
@@ -3397,10 +4891,10 @@
       <c r="K8" t="n">
         <v>2163</v>
       </c>
-      <c r="L8" s="3" t="n">
+      <c r="L8" s="11" t="n">
         <v>6.5</v>
       </c>
-      <c r="M8" s="3" t="n">
+      <c r="M8" s="11" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -3442,22 +4936,22 @@
       <c r="K9" t="n">
         <v>2878</v>
       </c>
-      <c r="L9" s="3" t="n">
+      <c r="L9" s="11" t="n">
         <v>6.5</v>
       </c>
-      <c r="M9" s="3" t="n">
+      <c r="M9" s="11" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>edge mixes: mean 3.6%  worst 5.8%  n=3</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>"pred (QEMU)" uses no silicon counter for the mix: per-application activity from QEMU scaled by each application's solo iteration rate. "pred (PMU)" re-runs the same model on silicon-measured activity, isolating model error from emulator error.</t>
         </is>
@@ -3468,13 +4962,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -3534,7 +5028,7 @@
           <t>vdd_arm</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="12" t="n">
         <v>11.4</v>
       </c>
       <c r="D2" t="n">
@@ -3561,7 +5055,7 @@
           <t>vdd_soc</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" s="11" t="n">
         <v>4.1</v>
       </c>
       <c r="D3" t="n">
@@ -3588,7 +5082,7 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="11" t="n">
         <v>6.4</v>
       </c>
       <c r="D4" t="n">
@@ -3607,59 +5101,86 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>edge mixes (concurrent)</t>
+          <t>activity: instructions</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SUM</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>3.6</v>
+          <t>QEMU vs PMU</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>1.75</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0.65</v>
       </c>
       <c r="E5" t="n">
-        <v>5.8</v>
+        <v>5.07</v>
       </c>
       <c r="F5" t="n">
-        <v>5.8</v>
+        <v>15.42</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>edge mixes (concurrent)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="F6" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="G6" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>all mixes (concurrent)</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>SUM</t>
         </is>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="C7" s="11" t="n">
         <v>4.8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D7" t="n">
         <v>5.8</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E7" t="n">
         <v>6.5</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>6.5</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G7" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="8" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>rails MEASURED on IMX95LPD5EVK-19 via NXP BCU (busy-window median, see busywin.py); A55 die 40-41 C under load; activity DERIVED from QEMU TCG plugins</t>
         </is>

--- a/xcheck/RESULTS-50.xlsx
+++ b/xcheck/RESULTS-50.xlsx
@@ -10,7 +10,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="activity factors" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="50 apps (single)" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="multi-app (concurrent)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bandwidth corner" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -101,13 +102,13 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -474,17 +475,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="11" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -510,20 +512,25 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>QEMU GB/s</t>
+          <t>QEMU read GB/s</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>silicon GB/s</t>
+          <t>silicon read GB/s</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>bandwidth err %</t>
+          <t>read err %</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>QEMU total GB/s (model input)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>elapsed s</t>
         </is>
@@ -545,15 +552,18 @@
         <v>-2</v>
       </c>
       <c r="E2" s="5" t="n">
-        <v>4.931</v>
+        <v>2.469</v>
       </c>
       <c r="F2" s="5" t="n">
         <v>2.531</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>94.8</v>
-      </c>
-      <c r="H2" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="H2" s="5" t="n">
+        <v>4.931</v>
+      </c>
+      <c r="I2" t="n">
         <v>0.22</v>
       </c>
     </row>
@@ -573,15 +583,18 @@
         <v>-1.69</v>
       </c>
       <c r="E3" s="5" t="n">
-        <v>4.661</v>
+        <v>2.332</v>
       </c>
       <c r="F3" s="5" t="n">
         <v>2.617</v>
       </c>
       <c r="G3" s="6" t="n">
-        <v>78.09999999999999</v>
-      </c>
-      <c r="H3" t="n">
+        <v>-10.9</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>4.661</v>
+      </c>
+      <c r="I3" t="n">
         <v>0.17</v>
       </c>
     </row>
@@ -606,10 +619,13 @@
       <c r="F4" s="5" t="n">
         <v>0.598</v>
       </c>
-      <c r="G4" s="6" t="n">
+      <c r="G4" s="7" t="n">
         <v>148.7</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4" s="5" t="n">
+        <v>1.486</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.92</v>
       </c>
     </row>
@@ -629,15 +645,18 @@
         <v>-1.2</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.025</v>
+        <v>0.024</v>
       </c>
       <c r="F5" s="5" t="n">
         <v>0.027</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="H5" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.41</v>
       </c>
     </row>
@@ -657,15 +676,18 @@
         <v>-1.53</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.424</v>
+        <v>0.239</v>
       </c>
       <c r="F6" s="5" t="n">
         <v>0.196</v>
       </c>
       <c r="G6" t="n">
-        <v>116.8</v>
-      </c>
-      <c r="H6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="I6" t="n">
         <v>17.63</v>
       </c>
     </row>
@@ -690,10 +712,13 @@
       <c r="F7" s="5" t="n">
         <v>0.32</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7" s="8" t="n">
         <v>-36.7</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7" s="5" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.72</v>
       </c>
     </row>
@@ -713,15 +738,18 @@
         <v>-0.3</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.168</v>
+        <v>0.16</v>
       </c>
       <c r="F8" s="5" t="n">
         <v>0.083</v>
       </c>
       <c r="G8" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="H8" t="n">
+        <v>92.8</v>
+      </c>
+      <c r="H8" s="5" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="I8" t="n">
         <v>4.56</v>
       </c>
     </row>
@@ -737,19 +765,22 @@
       <c r="C9" s="3" t="n">
         <v>304138792</v>
       </c>
-      <c r="D9" s="7" t="n">
+      <c r="D9" s="9" t="n">
         <v>-7.46</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.418</v>
+        <v>0.382</v>
       </c>
       <c r="F9" s="5" t="n">
         <v>0.312</v>
       </c>
-      <c r="G9" t="n">
-        <v>33.9</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G9" s="6" t="n">
+        <v>22.3</v>
+      </c>
+      <c r="H9" s="5" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -769,15 +800,18 @@
         <v>-0.53</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.7</v>
+        <v>0.573</v>
       </c>
       <c r="F10" s="5" t="n">
         <v>0.31</v>
       </c>
-      <c r="G10" t="n">
-        <v>125.6</v>
-      </c>
-      <c r="H10" t="n">
+      <c r="G10" s="7" t="n">
+        <v>84.40000000000001</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.29</v>
       </c>
     </row>
@@ -797,15 +831,18 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.076</v>
+        <v>0.064</v>
       </c>
       <c r="F11" s="5" t="n">
         <v>0.045</v>
       </c>
       <c r="G11" t="n">
-        <v>68.09999999999999</v>
-      </c>
-      <c r="H11" t="n">
+        <v>41.6</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -831,9 +868,12 @@
         <v>0.004</v>
       </c>
       <c r="G12" t="n">
-        <v>1452.2</v>
-      </c>
-      <c r="H12" t="n">
+        <v>1451.1</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.13</v>
       </c>
     </row>
@@ -853,15 +893,18 @@
         <v>-0.42</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.012</v>
+        <v>0.007</v>
       </c>
       <c r="F13" s="5" t="n">
         <v>0.01</v>
       </c>
       <c r="G13" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="H13" t="n">
+        <v>-30.8</v>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="I13" t="n">
         <v>1.31</v>
       </c>
     </row>
@@ -881,15 +924,18 @@
         <v>-1.49</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.099</v>
+        <v>0.002</v>
       </c>
       <c r="F14" s="5" t="n">
         <v>0.102</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.6</v>
-      </c>
-      <c r="H14" t="n">
+        <v>-98.2</v>
+      </c>
+      <c r="H14" s="5" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.26</v>
       </c>
     </row>
@@ -909,15 +955,18 @@
         <v>-1.11</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.254</v>
+        <v>0.153</v>
       </c>
       <c r="F15" s="5" t="n">
         <v>0.095</v>
       </c>
       <c r="G15" t="n">
-        <v>167.1</v>
-      </c>
-      <c r="H15" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="H15" s="5" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.15</v>
       </c>
     </row>
@@ -937,15 +986,18 @@
         <v>-0.45</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.021</v>
+        <v>0.016</v>
       </c>
       <c r="F16" s="5" t="n">
         <v>0.021</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H16" t="n">
+        <v>-21</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>0.021</v>
+      </c>
+      <c r="I16" t="n">
         <v>3.03</v>
       </c>
     </row>
@@ -961,7 +1013,7 @@
       <c r="C17" s="3" t="n">
         <v>832539047</v>
       </c>
-      <c r="D17" s="8" t="n">
+      <c r="D17" s="10" t="n">
         <v>-12.55</v>
       </c>
       <c r="E17" s="5" t="n">
@@ -971,9 +1023,12 @@
         <v>0.037</v>
       </c>
       <c r="G17" t="n">
-        <v>-99.5</v>
-      </c>
-      <c r="H17" t="n">
+        <v>-99.59999999999999</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.45</v>
       </c>
     </row>
@@ -999,9 +1054,12 @@
         <v>0.003</v>
       </c>
       <c r="G18" t="n">
-        <v>1531.4</v>
-      </c>
-      <c r="H18" t="n">
+        <v>1531.2</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -1017,7 +1075,7 @@
       <c r="C19" s="3" t="n">
         <v>440482683</v>
       </c>
-      <c r="D19" s="7" t="n">
+      <c r="D19" s="9" t="n">
         <v>-4.35</v>
       </c>
       <c r="E19" s="5" t="n">
@@ -1027,9 +1085,12 @@
         <v>0.148</v>
       </c>
       <c r="G19" t="n">
-        <v>-99.7</v>
-      </c>
-      <c r="H19" t="n">
+        <v>-99.8</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.2</v>
       </c>
     </row>
@@ -1049,15 +1110,18 @@
         <v>0.21</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.039</v>
+        <v>0.037</v>
       </c>
       <c r="F20" s="5" t="n">
         <v>0.046</v>
       </c>
       <c r="G20" t="n">
-        <v>-14.9</v>
-      </c>
-      <c r="H20" t="n">
+        <v>-19.4</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>0.039</v>
+      </c>
+      <c r="I20" t="n">
         <v>2.93</v>
       </c>
     </row>
@@ -1077,15 +1141,18 @@
         <v>-0.8</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.37</v>
+        <v>0.159</v>
       </c>
       <c r="F21" s="5" t="n">
         <v>0.223</v>
       </c>
       <c r="G21" t="n">
-        <v>66</v>
-      </c>
-      <c r="H21" t="n">
+        <v>-28.8</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.32</v>
       </c>
     </row>
@@ -1101,19 +1168,22 @@
       <c r="C22" s="3" t="n">
         <v>16783191876</v>
       </c>
-      <c r="D22" s="7" t="n">
+      <c r="D22" s="9" t="n">
         <v>-2.1</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.049</v>
+        <v>0.043</v>
       </c>
       <c r="F22" s="5" t="n">
         <v>0.045</v>
       </c>
       <c r="G22" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="H22" t="n">
+        <v>-5.8</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="I22" t="n">
         <v>9.33</v>
       </c>
     </row>
@@ -1133,15 +1203,18 @@
         <v>-0.21</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.159</v>
+        <v>0.157</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>0.233</v>
       </c>
       <c r="G23" t="n">
-        <v>-32</v>
-      </c>
-      <c r="H23" t="n">
+        <v>-32.8</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="I23" t="n">
         <v>6.07</v>
       </c>
     </row>
@@ -1169,7 +1242,10 @@
       <c r="G24" t="n">
         <v>-99.5</v>
       </c>
-      <c r="H24" t="n">
+      <c r="H24" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -1195,9 +1271,12 @@
         <v>0.001</v>
       </c>
       <c r="G25" t="n">
-        <v>1159.8</v>
-      </c>
-      <c r="H25" t="n">
+        <v>1159.4</v>
+      </c>
+      <c r="H25" s="5" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.91</v>
       </c>
     </row>
@@ -1223,9 +1302,12 @@
         <v>0.018</v>
       </c>
       <c r="G26" t="n">
-        <v>-99.09999999999999</v>
-      </c>
-      <c r="H26" t="n">
+        <v>-99.5</v>
+      </c>
+      <c r="H26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
         <v>2.41</v>
       </c>
     </row>
@@ -1251,9 +1333,12 @@
         <v>0.015</v>
       </c>
       <c r="G27" t="n">
-        <v>-98.3</v>
-      </c>
-      <c r="H27" t="n">
+        <v>-98.7</v>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
         <v>1.08</v>
       </c>
     </row>
@@ -1273,15 +1358,18 @@
         <v>-0.23</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.408</v>
+        <v>0.209</v>
       </c>
       <c r="F28" s="5" t="n">
         <v>0.118</v>
       </c>
       <c r="G28" t="n">
-        <v>244.7</v>
-      </c>
-      <c r="H28" t="n">
+        <v>76.59999999999999</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="I28" t="n">
         <v>1.54</v>
       </c>
     </row>
@@ -1301,15 +1389,18 @@
         <v>-0.15</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>0.036</v>
+        <v>0.023</v>
       </c>
       <c r="F29" s="5" t="n">
         <v>0.022</v>
       </c>
       <c r="G29" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="H29" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="I29" t="n">
         <v>2.18</v>
       </c>
     </row>
@@ -1335,9 +1426,12 @@
         <v>0.002</v>
       </c>
       <c r="G30" t="n">
-        <v>2038.7</v>
-      </c>
-      <c r="H30" t="n">
+        <v>2038.6</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="I30" t="n">
         <v>2.84</v>
       </c>
     </row>
@@ -1353,7 +1447,7 @@
       <c r="C31" s="3" t="n">
         <v>2666087519</v>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="9" t="n">
         <v>-2.88</v>
       </c>
       <c r="E31" s="5" t="n">
@@ -1363,9 +1457,12 @@
         <v>0.005</v>
       </c>
       <c r="G31" t="n">
-        <v>-98.3</v>
-      </c>
-      <c r="H31" t="n">
+        <v>-98.40000000000001</v>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>1.56</v>
       </c>
     </row>
@@ -1391,9 +1488,12 @@
         <v>0.043</v>
       </c>
       <c r="G32" t="n">
-        <v>-99.7</v>
-      </c>
-      <c r="H32" t="n">
+        <v>-99.8</v>
+      </c>
+      <c r="H32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.66</v>
       </c>
     </row>
@@ -1413,15 +1513,18 @@
         <v>-0.46</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.325</v>
+        <v>0.17</v>
       </c>
       <c r="F33" s="5" t="n">
         <v>0.089</v>
       </c>
       <c r="G33" t="n">
-        <v>265.2</v>
-      </c>
-      <c r="H33" t="n">
+        <v>91.09999999999999</v>
+      </c>
+      <c r="H33" s="5" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="I33" t="n">
         <v>0.96</v>
       </c>
     </row>
@@ -1447,9 +1550,12 @@
         <v>0.015</v>
       </c>
       <c r="G34" t="n">
-        <v>-86.2</v>
-      </c>
-      <c r="H34" t="n">
+        <v>-89.2</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="I34" t="n">
         <v>0.08</v>
       </c>
     </row>
@@ -1469,15 +1575,18 @@
         <v>-0.18</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="F35" s="5" t="n">
         <v>0.012</v>
       </c>
       <c r="G35" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="H35" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="H35" s="5" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="I35" t="n">
         <v>2.07</v>
       </c>
     </row>
@@ -1505,7 +1614,10 @@
       <c r="G36" t="n">
         <v>-99.7</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H36" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.4</v>
       </c>
     </row>
@@ -1531,9 +1643,12 @@
         <v>0.006</v>
       </c>
       <c r="G37" t="n">
-        <v>1775.8</v>
-      </c>
-      <c r="H37" t="n">
+        <v>1775.7</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.64</v>
       </c>
     </row>
@@ -1549,7 +1664,7 @@
       <c r="C38" s="3" t="n">
         <v>319977828</v>
       </c>
-      <c r="D38" s="8" t="n">
+      <c r="D38" s="10" t="n">
         <v>-15.42</v>
       </c>
       <c r="E38" s="5" t="n">
@@ -1559,9 +1674,12 @@
         <v>0.09</v>
       </c>
       <c r="G38" t="n">
-        <v>-99.59999999999999</v>
-      </c>
-      <c r="H38" t="n">
+        <v>-99.7</v>
+      </c>
+      <c r="H38" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.23</v>
       </c>
     </row>
@@ -1581,15 +1699,18 @@
         <v>-0.22</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0.023</v>
+        <v>0.017</v>
       </c>
       <c r="F39" s="5" t="n">
         <v>0.014</v>
       </c>
       <c r="G39" t="n">
-        <v>63.6</v>
-      </c>
-      <c r="H39" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="H39" s="5" t="n">
+        <v>0.023</v>
+      </c>
+      <c r="I39" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1609,15 +1730,18 @@
         <v>-1.84</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.291</v>
+        <v>0.276</v>
       </c>
       <c r="F40" s="5" t="n">
         <v>0.23</v>
       </c>
       <c r="G40" t="n">
-        <v>26.2</v>
-      </c>
-      <c r="H40" t="n">
+        <v>20</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="I40" t="n">
         <v>1.28</v>
       </c>
     </row>
@@ -1643,9 +1767,12 @@
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>-77.40000000000001</v>
-      </c>
-      <c r="H41" t="n">
+        <v>-78.40000000000001</v>
+      </c>
+      <c r="H41" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" t="n">
         <v>0.54</v>
       </c>
     </row>
@@ -1671,9 +1798,12 @@
         <v>0.001</v>
       </c>
       <c r="G42" t="n">
-        <v>-89.59999999999999</v>
-      </c>
-      <c r="H42" t="n">
+        <v>-94</v>
+      </c>
+      <c r="H42" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" t="n">
         <v>14.26</v>
       </c>
     </row>
@@ -1689,19 +1819,22 @@
       <c r="C43" s="3" t="n">
         <v>2001005821</v>
       </c>
-      <c r="D43" s="7" t="n">
+      <c r="D43" s="9" t="n">
         <v>-5.21</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.364</v>
+        <v>0.352</v>
       </c>
       <c r="F43" s="5" t="n">
         <v>0.317</v>
       </c>
-      <c r="G43" t="n">
-        <v>14.7</v>
-      </c>
-      <c r="H43" t="n">
+      <c r="G43" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="H43" s="5" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="I43" t="n">
         <v>1.84</v>
       </c>
     </row>
@@ -1727,9 +1860,12 @@
         <v>0.024</v>
       </c>
       <c r="G44" t="n">
-        <v>-98.2</v>
-      </c>
-      <c r="H44" t="n">
+        <v>-98.7</v>
+      </c>
+      <c r="H44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
         <v>0.67</v>
       </c>
     </row>
@@ -1755,9 +1891,12 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>-66.59999999999999</v>
-      </c>
-      <c r="H45" t="n">
+        <v>-68</v>
+      </c>
+      <c r="H45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
         <v>0.53</v>
       </c>
     </row>
@@ -1783,9 +1922,12 @@
         <v>0.001</v>
       </c>
       <c r="G46" t="n">
-        <v>-88.5</v>
-      </c>
-      <c r="H46" t="n">
+        <v>-93.5</v>
+      </c>
+      <c r="H46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
         <v>10.49</v>
       </c>
     </row>
@@ -1805,15 +1947,18 @@
         <v>-1.29</v>
       </c>
       <c r="E47" s="5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.044</v>
       </c>
       <c r="F47" s="5" t="n">
         <v>0.04</v>
       </c>
       <c r="G47" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="H47" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I47" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -1839,9 +1984,12 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>-5.4</v>
-      </c>
-      <c r="H48" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
         <v>0.36</v>
       </c>
     </row>
@@ -1867,9 +2015,12 @@
         <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>-74.8</v>
-      </c>
-      <c r="H49" t="n">
+        <v>-76</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
         <v>0.67</v>
       </c>
     </row>
@@ -1885,19 +2036,22 @@
       <c r="C50" s="3" t="n">
         <v>203929213</v>
       </c>
-      <c r="D50" s="7" t="n">
+      <c r="D50" s="9" t="n">
         <v>5.07</v>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.464</v>
+        <v>0.447</v>
       </c>
       <c r="F50" s="5" t="n">
         <v>0.452</v>
       </c>
-      <c r="G50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="H50" t="n">
+      <c r="G50" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="I50" t="n">
         <v>4.14</v>
       </c>
     </row>
@@ -1913,38 +2067,41 @@
       <c r="C51" s="3" t="n">
         <v>328404010</v>
       </c>
-      <c r="D51" s="7" t="n">
+      <c r="D51" s="9" t="n">
         <v>-3.63</v>
       </c>
       <c r="E51" s="5" t="n">
-        <v>0.481</v>
+        <v>0.45</v>
       </c>
       <c r="F51" s="5" t="n">
         <v>0.454</v>
       </c>
-      <c r="G51" t="n">
-        <v>6</v>
-      </c>
-      <c r="H51" t="n">
+      <c r="G51" s="6" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H51" s="5" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="I51" t="n">
         <v>4.33</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>instructions: MAPE 1.75%, median 0.65%, 41 of 50 within 2%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="10" t="inlineStr">
-        <is>
-          <t>bandwidth error is only meaningful for the 3 applications above 0.5 GB/s; below that the absolute traffic is too small for the ratio to mean anything</t>
+      <c r="A54" s="12" t="inlineStr">
+        <is>
+          <t>l3d_cache_refill is a REFILL counter and sees READS; the like-for-like QEMU quantity is dram_read_proxy. The model is driven by TOTAL traffic (last column), which is the quantity its coefficient was calibrated against.</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="10" t="inlineStr">
+      <c r="A55" s="12" t="inlineStr">
         <is>
           <t>QEMU counts DERIVED from TCG plugins (linux-user); silicon counts MEASURED via ARM PMU (i.MX95, A55 core 0, pinned 1.8 GHz)</t>
         </is>
@@ -2076,7 +2233,7 @@
       <c r="E2" t="n">
         <v>788</v>
       </c>
-      <c r="F2" s="11" t="n">
+      <c r="F2" s="6" t="n">
         <v>3.6</v>
       </c>
       <c r="G2" t="n">
@@ -2085,7 +2242,7 @@
       <c r="H2" t="n">
         <v>979.2</v>
       </c>
-      <c r="I2" s="11" t="n">
+      <c r="I2" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="J2" t="n">
@@ -2094,7 +2251,7 @@
       <c r="K2" t="n">
         <v>1767.2</v>
       </c>
-      <c r="L2" s="11" t="n">
+      <c r="L2" s="6" t="n">
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
@@ -2127,7 +2284,7 @@
       <c r="E3" t="n">
         <v>804.8</v>
       </c>
-      <c r="F3" s="11" t="n">
+      <c r="F3" s="6" t="n">
         <v>1.3</v>
       </c>
       <c r="G3" t="n">
@@ -2136,7 +2293,7 @@
       <c r="H3" t="n">
         <v>990.6</v>
       </c>
-      <c r="I3" s="11" t="n">
+      <c r="I3" s="6" t="n">
         <v>4.2</v>
       </c>
       <c r="J3" t="n">
@@ -2145,7 +2302,7 @@
       <c r="K3" t="n">
         <v>1795.3</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L3" s="6" t="n">
         <v>2.9</v>
       </c>
       <c r="M3" t="n">
@@ -2178,7 +2335,7 @@
       <c r="E4" t="n">
         <v>626.5</v>
       </c>
-      <c r="F4" s="12" t="n">
+      <c r="F4" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="G4" t="n">
@@ -2187,7 +2344,7 @@
       <c r="H4" t="n">
         <v>931.1</v>
       </c>
-      <c r="I4" s="11" t="n">
+      <c r="I4" s="6" t="n">
         <v>5.1</v>
       </c>
       <c r="J4" t="n">
@@ -2196,7 +2353,7 @@
       <c r="K4" t="n">
         <v>1557.6</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="6" t="n">
         <v>7</v>
       </c>
       <c r="M4" t="n">
@@ -2229,7 +2386,7 @@
       <c r="E5" t="n">
         <v>631.9</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="7" t="n">
         <v>22.8</v>
       </c>
       <c r="G5" t="n">
@@ -2238,7 +2395,7 @@
       <c r="H5" t="n">
         <v>897.1</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="6" t="n">
         <v>4.8</v>
       </c>
       <c r="J5" t="n">
@@ -2247,7 +2404,7 @@
       <c r="K5" t="n">
         <v>1529</v>
       </c>
-      <c r="L5" s="6" t="n">
+      <c r="L5" s="7" t="n">
         <v>12.2</v>
       </c>
       <c r="M5" t="n">
@@ -2280,7 +2437,7 @@
       <c r="E6" t="n">
         <v>597</v>
       </c>
-      <c r="F6" s="6" t="n">
+      <c r="F6" s="7" t="n">
         <v>17</v>
       </c>
       <c r="G6" t="n">
@@ -2289,7 +2446,7 @@
       <c r="H6" t="n">
         <v>915</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="6" t="n">
         <v>5.8</v>
       </c>
       <c r="J6" t="n">
@@ -2298,7 +2455,7 @@
       <c r="K6" t="n">
         <v>1512</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="8" t="n">
         <v>10.2</v>
       </c>
       <c r="M6" t="n">
@@ -2331,7 +2488,7 @@
       <c r="E7" t="n">
         <v>609.8</v>
       </c>
-      <c r="F7" s="6" t="n">
+      <c r="F7" s="7" t="n">
         <v>19.9</v>
       </c>
       <c r="G7" t="n">
@@ -2340,7 +2497,7 @@
       <c r="H7" t="n">
         <v>904.9</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="6" t="n">
         <v>5.3</v>
       </c>
       <c r="J7" t="n">
@@ -2349,7 +2506,7 @@
       <c r="K7" t="n">
         <v>1514.7</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="8" t="n">
         <v>11.2</v>
       </c>
       <c r="M7" t="n">
@@ -2382,7 +2539,7 @@
       <c r="E8" t="n">
         <v>691.2</v>
       </c>
-      <c r="F8" s="6" t="n">
+      <c r="F8" s="7" t="n">
         <v>25.2</v>
       </c>
       <c r="G8" t="n">
@@ -2391,7 +2548,7 @@
       <c r="H8" t="n">
         <v>922.9</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="6" t="n">
         <v>7.1</v>
       </c>
       <c r="J8" t="n">
@@ -2400,7 +2557,7 @@
       <c r="K8" t="n">
         <v>1614.2</v>
       </c>
-      <c r="L8" s="6" t="n">
+      <c r="L8" s="7" t="n">
         <v>14.8</v>
       </c>
       <c r="M8" t="n">
@@ -2433,7 +2590,7 @@
       <c r="E9" t="n">
         <v>647.1</v>
       </c>
-      <c r="F9" s="6" t="n">
+      <c r="F9" s="7" t="n">
         <v>23.1</v>
       </c>
       <c r="G9" t="n">
@@ -2442,7 +2599,7 @@
       <c r="H9" t="n">
         <v>917.5</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="6" t="n">
         <v>6.1</v>
       </c>
       <c r="J9" t="n">
@@ -2451,7 +2608,7 @@
       <c r="K9" t="n">
         <v>1564.6</v>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="L9" s="7" t="n">
         <v>13.1</v>
       </c>
       <c r="M9" t="n">
@@ -2484,7 +2641,7 @@
       <c r="E10" t="n">
         <v>601.8</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="6" t="n">
         <v>7.6</v>
       </c>
       <c r="G10" t="n">
@@ -2493,7 +2650,7 @@
       <c r="H10" t="n">
         <v>922.8</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="6" t="n">
         <v>5.9</v>
       </c>
       <c r="J10" t="n">
@@ -2502,7 +2659,7 @@
       <c r="K10" t="n">
         <v>1524.6</v>
       </c>
-      <c r="L10" s="11" t="n">
+      <c r="L10" s="6" t="n">
         <v>6.6</v>
       </c>
       <c r="M10" t="n">
@@ -2535,7 +2692,7 @@
       <c r="E11" t="n">
         <v>585.9</v>
       </c>
-      <c r="F11" s="6" t="n">
+      <c r="F11" s="7" t="n">
         <v>13.4</v>
       </c>
       <c r="G11" t="n">
@@ -2544,7 +2701,7 @@
       <c r="H11" t="n">
         <v>871</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="6" t="n">
         <v>1.8</v>
       </c>
       <c r="J11" t="n">
@@ -2553,7 +2710,7 @@
       <c r="K11" t="n">
         <v>1456.9</v>
       </c>
-      <c r="L11" s="11" t="n">
+      <c r="L11" s="6" t="n">
         <v>6.5</v>
       </c>
       <c r="M11" t="n">
@@ -2586,7 +2743,7 @@
       <c r="E12" t="n">
         <v>609.4</v>
       </c>
-      <c r="F12" s="6" t="n">
+      <c r="F12" s="7" t="n">
         <v>14.9</v>
       </c>
       <c r="G12" t="n">
@@ -2595,7 +2752,7 @@
       <c r="H12" t="n">
         <v>907.5</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="6" t="n">
         <v>5.7</v>
       </c>
       <c r="J12" t="n">
@@ -2604,7 +2761,7 @@
       <c r="K12" t="n">
         <v>1516.9</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L12" s="8" t="n">
         <v>9.4</v>
       </c>
       <c r="M12" t="n">
@@ -2637,7 +2794,7 @@
       <c r="E13" t="n">
         <v>580.4</v>
       </c>
-      <c r="F13" s="6" t="n">
+      <c r="F13" s="7" t="n">
         <v>14.4</v>
       </c>
       <c r="G13" t="n">
@@ -2646,7 +2803,7 @@
       <c r="H13" t="n">
         <v>851.5</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="I13" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="J13" t="n">
@@ -2655,7 +2812,7 @@
       <c r="K13" t="n">
         <v>1431.9</v>
       </c>
-      <c r="L13" s="11" t="n">
+      <c r="L13" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="M13" t="n">
@@ -2688,7 +2845,7 @@
       <c r="E14" t="n">
         <v>569.1</v>
       </c>
-      <c r="F14" s="6" t="n">
+      <c r="F14" s="7" t="n">
         <v>15.5</v>
       </c>
       <c r="G14" t="n">
@@ -2697,7 +2854,7 @@
       <c r="H14" t="n">
         <v>908.2</v>
       </c>
-      <c r="I14" s="11" t="n">
+      <c r="I14" s="6" t="n">
         <v>5.8</v>
       </c>
       <c r="J14" t="n">
@@ -2706,7 +2863,7 @@
       <c r="K14" t="n">
         <v>1477.3</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="L14" s="8" t="n">
         <v>9.6</v>
       </c>
       <c r="M14" t="n">
@@ -2739,7 +2896,7 @@
       <c r="E15" t="n">
         <v>612.9</v>
       </c>
-      <c r="F15" s="6" t="n">
+      <c r="F15" s="7" t="n">
         <v>12.4</v>
       </c>
       <c r="G15" t="n">
@@ -2748,7 +2905,7 @@
       <c r="H15" t="n">
         <v>911.4</v>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="I15" s="6" t="n">
         <v>5.7</v>
       </c>
       <c r="J15" t="n">
@@ -2757,7 +2914,7 @@
       <c r="K15" t="n">
         <v>1524.3</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="L15" s="8" t="n">
         <v>8.4</v>
       </c>
       <c r="M15" t="n">
@@ -2790,7 +2947,7 @@
       <c r="E16" t="n">
         <v>575.6</v>
       </c>
-      <c r="F16" s="6" t="n">
+      <c r="F16" s="7" t="n">
         <v>13.9</v>
       </c>
       <c r="G16" t="n">
@@ -2799,7 +2956,7 @@
       <c r="H16" t="n">
         <v>858</v>
       </c>
-      <c r="I16" s="11" t="n">
+      <c r="I16" s="6" t="n">
         <v>0.4</v>
       </c>
       <c r="J16" t="n">
@@ -2808,7 +2965,7 @@
       <c r="K16" t="n">
         <v>1433.6</v>
       </c>
-      <c r="L16" s="11" t="n">
+      <c r="L16" s="6" t="n">
         <v>5.8</v>
       </c>
       <c r="M16" t="n">
@@ -2841,7 +2998,7 @@
       <c r="E17" t="n">
         <v>572.9</v>
       </c>
-      <c r="F17" s="6" t="n">
+      <c r="F17" s="7" t="n">
         <v>15.9</v>
       </c>
       <c r="G17" t="n">
@@ -2850,7 +3007,7 @@
       <c r="H17" t="n">
         <v>902.7</v>
       </c>
-      <c r="I17" s="11" t="n">
+      <c r="I17" s="6" t="n">
         <v>5.5</v>
       </c>
       <c r="J17" t="n">
@@ -2859,7 +3016,7 @@
       <c r="K17" t="n">
         <v>1475.6</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="L17" s="8" t="n">
         <v>9.5</v>
       </c>
       <c r="M17" t="n">
@@ -2892,7 +3049,7 @@
       <c r="E18" t="n">
         <v>572.6</v>
       </c>
-      <c r="F18" s="11" t="n">
+      <c r="F18" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="G18" t="n">
@@ -2901,7 +3058,7 @@
       <c r="H18" t="n">
         <v>903.4</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="6" t="n">
         <v>5.2</v>
       </c>
       <c r="J18" t="n">
@@ -2910,7 +3067,7 @@
       <c r="K18" t="n">
         <v>1476</v>
       </c>
-      <c r="L18" s="11" t="n">
+      <c r="L18" s="6" t="n">
         <v>5.4</v>
       </c>
       <c r="M18" t="n">
@@ -2943,7 +3100,7 @@
       <c r="E19" t="n">
         <v>578.6</v>
       </c>
-      <c r="F19" s="6" t="n">
+      <c r="F19" s="7" t="n">
         <v>12.9</v>
       </c>
       <c r="G19" t="n">
@@ -2952,7 +3109,7 @@
       <c r="H19" t="n">
         <v>905</v>
       </c>
-      <c r="I19" s="11" t="n">
+      <c r="I19" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="J19" t="n">
@@ -2961,7 +3118,7 @@
       <c r="K19" t="n">
         <v>1483.6</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="L19" s="8" t="n">
         <v>8.5</v>
       </c>
       <c r="M19" t="n">
@@ -2994,7 +3151,7 @@
       <c r="E20" t="n">
         <v>574.3</v>
       </c>
-      <c r="F20" s="6" t="n">
+      <c r="F20" s="7" t="n">
         <v>13.9</v>
       </c>
       <c r="G20" t="n">
@@ -3003,7 +3160,7 @@
       <c r="H20" t="n">
         <v>894.8</v>
       </c>
-      <c r="I20" s="11" t="n">
+      <c r="I20" s="6" t="n">
         <v>4.5</v>
       </c>
       <c r="J20" t="n">
@@ -3012,7 +3169,7 @@
       <c r="K20" t="n">
         <v>1469.1</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L20" s="8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="M20" t="n">
@@ -3045,7 +3202,7 @@
       <c r="E21" t="n">
         <v>587.1</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <v>12.1</v>
       </c>
       <c r="G21" t="n">
@@ -3054,7 +3211,7 @@
       <c r="H21" t="n">
         <v>919.2</v>
       </c>
-      <c r="I21" s="11" t="n">
+      <c r="I21" s="6" t="n">
         <v>6.3</v>
       </c>
       <c r="J21" t="n">
@@ -3063,7 +3220,7 @@
       <c r="K21" t="n">
         <v>1506.4</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="8" t="n">
         <v>8.6</v>
       </c>
       <c r="M21" t="n">
@@ -3096,7 +3253,7 @@
       <c r="E22" t="n">
         <v>549</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="F22" s="8" t="n">
         <v>10.7</v>
       </c>
       <c r="G22" t="n">
@@ -3105,7 +3262,7 @@
       <c r="H22" t="n">
         <v>888.7</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="6" t="n">
         <v>3.8</v>
       </c>
       <c r="J22" t="n">
@@ -3114,7 +3271,7 @@
       <c r="K22" t="n">
         <v>1437.7</v>
       </c>
-      <c r="L22" s="11" t="n">
+      <c r="L22" s="6" t="n">
         <v>6.4</v>
       </c>
       <c r="M22" t="n">
@@ -3147,7 +3304,7 @@
       <c r="E23" t="n">
         <v>537.9</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="F23" s="8" t="n">
         <v>10.6</v>
       </c>
       <c r="G23" t="n">
@@ -3156,7 +3313,7 @@
       <c r="H23" t="n">
         <v>906.5</v>
       </c>
-      <c r="I23" s="11" t="n">
+      <c r="I23" s="6" t="n">
         <v>5.5</v>
       </c>
       <c r="J23" t="n">
@@ -3165,7 +3322,7 @@
       <c r="K23" t="n">
         <v>1444.4</v>
       </c>
-      <c r="L23" s="11" t="n">
+      <c r="L23" s="6" t="n">
         <v>7.4</v>
       </c>
       <c r="M23" t="n">
@@ -3198,7 +3355,7 @@
       <c r="E24" t="n">
         <v>570.5</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="F24" s="8" t="n">
         <v>9.4</v>
       </c>
       <c r="G24" t="n">
@@ -3207,7 +3364,7 @@
       <c r="H24" t="n">
         <v>896.8</v>
       </c>
-      <c r="I24" s="11" t="n">
+      <c r="I24" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="J24" t="n">
@@ -3216,7 +3373,7 @@
       <c r="K24" t="n">
         <v>1467.4</v>
       </c>
-      <c r="L24" s="11" t="n">
+      <c r="L24" s="6" t="n">
         <v>6.5</v>
       </c>
       <c r="M24" t="n">
@@ -3249,7 +3406,7 @@
       <c r="E25" t="n">
         <v>544.5</v>
       </c>
-      <c r="F25" s="11" t="n">
+      <c r="F25" s="6" t="n">
         <v>3.9</v>
       </c>
       <c r="G25" t="n">
@@ -3258,7 +3415,7 @@
       <c r="H25" t="n">
         <v>900.7</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="I25" s="6" t="n">
         <v>5.1</v>
       </c>
       <c r="J25" t="n">
@@ -3267,7 +3424,7 @@
       <c r="K25" t="n">
         <v>1445.3</v>
       </c>
-      <c r="L25" s="11" t="n">
+      <c r="L25" s="6" t="n">
         <v>4.6</v>
       </c>
       <c r="M25" t="n">
@@ -3300,7 +3457,7 @@
       <c r="E26" t="n">
         <v>566.6</v>
       </c>
-      <c r="F26" s="6" t="n">
+      <c r="F26" s="7" t="n">
         <v>14.9</v>
       </c>
       <c r="G26" t="n">
@@ -3309,7 +3466,7 @@
       <c r="H26" t="n">
         <v>866.3</v>
       </c>
-      <c r="I26" s="11" t="n">
+      <c r="I26" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="J26" t="n">
@@ -3318,7 +3475,7 @@
       <c r="K26" t="n">
         <v>1433</v>
       </c>
-      <c r="L26" s="11" t="n">
+      <c r="L26" s="6" t="n">
         <v>6.8</v>
       </c>
       <c r="M26" t="n">
@@ -3351,7 +3508,7 @@
       <c r="E27" t="n">
         <v>563</v>
       </c>
-      <c r="F27" s="6" t="n">
+      <c r="F27" s="7" t="n">
         <v>13</v>
       </c>
       <c r="G27" t="n">
@@ -3360,7 +3517,7 @@
       <c r="H27" t="n">
         <v>862</v>
       </c>
-      <c r="I27" s="11" t="n">
+      <c r="I27" s="6" t="n">
         <v>1</v>
       </c>
       <c r="J27" t="n">
@@ -3369,7 +3526,7 @@
       <c r="K27" t="n">
         <v>1425</v>
       </c>
-      <c r="L27" s="11" t="n">
+      <c r="L27" s="6" t="n">
         <v>5.7</v>
       </c>
       <c r="M27" t="n">
@@ -3402,7 +3559,7 @@
       <c r="E28" t="n">
         <v>574.1</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="F28" s="8" t="n">
         <v>9.1</v>
       </c>
       <c r="G28" t="n">
@@ -3411,7 +3568,7 @@
       <c r="H28" t="n">
         <v>908.2</v>
       </c>
-      <c r="I28" s="11" t="n">
+      <c r="I28" s="6" t="n">
         <v>5.1</v>
       </c>
       <c r="J28" t="n">
@@ -3420,7 +3577,7 @@
       <c r="K28" t="n">
         <v>1482.3</v>
       </c>
-      <c r="L28" s="11" t="n">
+      <c r="L28" s="6" t="n">
         <v>6.6</v>
       </c>
       <c r="M28" t="n">
@@ -3453,7 +3610,7 @@
       <c r="E29" t="n">
         <v>532</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="F29" s="8" t="n">
         <v>10.3</v>
       </c>
       <c r="G29" t="n">
@@ -3462,7 +3619,7 @@
       <c r="H29" t="n">
         <v>902.4</v>
       </c>
-      <c r="I29" s="11" t="n">
+      <c r="I29" s="6" t="n">
         <v>5.4</v>
       </c>
       <c r="J29" t="n">
@@ -3471,7 +3628,7 @@
       <c r="K29" t="n">
         <v>1434.4</v>
       </c>
-      <c r="L29" s="11" t="n">
+      <c r="L29" s="6" t="n">
         <v>7.2</v>
       </c>
       <c r="M29" t="n">
@@ -3504,7 +3661,7 @@
       <c r="E30" t="n">
         <v>556.2</v>
       </c>
-      <c r="F30" s="11" t="n">
+      <c r="F30" s="6" t="n">
         <v>2.6</v>
       </c>
       <c r="G30" t="n">
@@ -3513,7 +3670,7 @@
       <c r="H30" t="n">
         <v>901.6</v>
       </c>
-      <c r="I30" s="11" t="n">
+      <c r="I30" s="6" t="n">
         <v>5</v>
       </c>
       <c r="J30" t="n">
@@ -3522,7 +3679,7 @@
       <c r="K30" t="n">
         <v>1457.8</v>
       </c>
-      <c r="L30" s="11" t="n">
+      <c r="L30" s="6" t="n">
         <v>4.1</v>
       </c>
       <c r="M30" t="n">
@@ -3555,7 +3712,7 @@
       <c r="E31" t="n">
         <v>561.3</v>
       </c>
-      <c r="F31" s="6" t="n">
+      <c r="F31" s="7" t="n">
         <v>13.9</v>
       </c>
       <c r="G31" t="n">
@@ -3564,7 +3721,7 @@
       <c r="H31" t="n">
         <v>866.8</v>
       </c>
-      <c r="I31" s="11" t="n">
+      <c r="I31" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="J31" t="n">
@@ -3573,7 +3730,7 @@
       <c r="K31" t="n">
         <v>1428.1</v>
       </c>
-      <c r="L31" s="11" t="n">
+      <c r="L31" s="6" t="n">
         <v>6.4</v>
       </c>
       <c r="M31" t="n">
@@ -3606,7 +3763,7 @@
       <c r="E32" t="n">
         <v>545.9</v>
       </c>
-      <c r="F32" s="11" t="n">
+      <c r="F32" s="6" t="n">
         <v>3.2</v>
       </c>
       <c r="G32" t="n">
@@ -3615,7 +3772,7 @@
       <c r="H32" t="n">
         <v>875.3</v>
       </c>
-      <c r="I32" s="11" t="n">
+      <c r="I32" s="6" t="n">
         <v>2.3</v>
       </c>
       <c r="J32" t="n">
@@ -3624,7 +3781,7 @@
       <c r="K32" t="n">
         <v>1421.2</v>
       </c>
-      <c r="L32" s="11" t="n">
+      <c r="L32" s="6" t="n">
         <v>2.7</v>
       </c>
       <c r="M32" t="n">
@@ -3657,7 +3814,7 @@
       <c r="E33" t="n">
         <v>570.3</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="F33" s="8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="G33" t="n">
@@ -3666,7 +3823,7 @@
       <c r="H33" t="n">
         <v>902.8</v>
       </c>
-      <c r="I33" s="11" t="n">
+      <c r="I33" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="J33" t="n">
@@ -3675,7 +3832,7 @@
       <c r="K33" t="n">
         <v>1473</v>
       </c>
-      <c r="L33" s="11" t="n">
+      <c r="L33" s="6" t="n">
         <v>6.5</v>
       </c>
       <c r="M33" t="n">
@@ -3708,7 +3865,7 @@
       <c r="E34" t="n">
         <v>603.1</v>
       </c>
-      <c r="F34" s="6" t="n">
+      <c r="F34" s="7" t="n">
         <v>19.1</v>
       </c>
       <c r="G34" t="n">
@@ -3717,7 +3874,7 @@
       <c r="H34" t="n">
         <v>875.3</v>
       </c>
-      <c r="I34" s="11" t="n">
+      <c r="I34" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="J34" t="n">
@@ -3726,7 +3883,7 @@
       <c r="K34" t="n">
         <v>1478.4</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="L34" s="8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="M34" t="n">
@@ -3759,7 +3916,7 @@
       <c r="E35" t="n">
         <v>520.3</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="F35" s="8" t="n">
         <v>10.8</v>
       </c>
       <c r="G35" t="n">
@@ -3768,7 +3925,7 @@
       <c r="H35" t="n">
         <v>897.6</v>
       </c>
-      <c r="I35" s="11" t="n">
+      <c r="I35" s="6" t="n">
         <v>5</v>
       </c>
       <c r="J35" t="n">
@@ -3777,7 +3934,7 @@
       <c r="K35" t="n">
         <v>1417.9</v>
       </c>
-      <c r="L35" s="11" t="n">
+      <c r="L35" s="6" t="n">
         <v>7.1</v>
       </c>
       <c r="M35" t="n">
@@ -3810,7 +3967,7 @@
       <c r="E36" t="n">
         <v>570</v>
       </c>
-      <c r="F36" s="11" t="n">
+      <c r="F36" s="6" t="n">
         <v>7.8</v>
       </c>
       <c r="G36" t="n">
@@ -3819,7 +3976,7 @@
       <c r="H36" t="n">
         <v>899.6</v>
       </c>
-      <c r="I36" s="11" t="n">
+      <c r="I36" s="6" t="n">
         <v>5</v>
       </c>
       <c r="J36" t="n">
@@ -3828,7 +3985,7 @@
       <c r="K36" t="n">
         <v>1469.6</v>
       </c>
-      <c r="L36" s="11" t="n">
+      <c r="L36" s="6" t="n">
         <v>6.1</v>
       </c>
       <c r="M36" t="n">
@@ -3861,7 +4018,7 @@
       <c r="E37" t="n">
         <v>572.3</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="F37" s="8" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="G37" t="n">
@@ -3870,7 +4027,7 @@
       <c r="H37" t="n">
         <v>905.5</v>
       </c>
-      <c r="I37" s="11" t="n">
+      <c r="I37" s="6" t="n">
         <v>5.4</v>
       </c>
       <c r="J37" t="n">
@@ -3879,7 +4036,7 @@
       <c r="K37" t="n">
         <v>1477.8</v>
       </c>
-      <c r="L37" s="11" t="n">
+      <c r="L37" s="6" t="n">
         <v>6.7</v>
       </c>
       <c r="M37" t="n">
@@ -3912,7 +4069,7 @@
       <c r="E38" t="n">
         <v>534.5</v>
       </c>
-      <c r="F38" s="6" t="n">
+      <c r="F38" s="7" t="n">
         <v>13.2</v>
       </c>
       <c r="G38" t="n">
@@ -3921,7 +4078,7 @@
       <c r="H38" t="n">
         <v>902.9</v>
       </c>
-      <c r="I38" s="11" t="n">
+      <c r="I38" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="J38" t="n">
@@ -3930,7 +4087,7 @@
       <c r="K38" t="n">
         <v>1437.4</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="L38" s="8" t="n">
         <v>8.4</v>
       </c>
       <c r="M38" t="n">
@@ -3963,7 +4120,7 @@
       <c r="E39" t="n">
         <v>541.6</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="F39" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="G39" t="n">
@@ -3972,7 +4129,7 @@
       <c r="H39" t="n">
         <v>898.1</v>
       </c>
-      <c r="I39" s="11" t="n">
+      <c r="I39" s="6" t="n">
         <v>4.9</v>
       </c>
       <c r="J39" t="n">
@@ -3981,7 +4138,7 @@
       <c r="K39" t="n">
         <v>1439.7</v>
       </c>
-      <c r="L39" s="11" t="n">
+      <c r="L39" s="6" t="n">
         <v>6.5</v>
       </c>
       <c r="M39" t="n">
@@ -4014,7 +4171,7 @@
       <c r="E40" t="n">
         <v>509.7</v>
       </c>
-      <c r="F40" s="11" t="n">
+      <c r="F40" s="6" t="n">
         <v>5.8</v>
       </c>
       <c r="G40" t="n">
@@ -4023,7 +4180,7 @@
       <c r="H40" t="n">
         <v>910.3</v>
       </c>
-      <c r="I40" s="11" t="n">
+      <c r="I40" s="6" t="n">
         <v>5.7</v>
       </c>
       <c r="J40" t="n">
@@ -4032,7 +4189,7 @@
       <c r="K40" t="n">
         <v>1420.1</v>
       </c>
-      <c r="L40" s="11" t="n">
+      <c r="L40" s="6" t="n">
         <v>5.7</v>
       </c>
       <c r="M40" t="n">
@@ -4065,7 +4222,7 @@
       <c r="E41" t="n">
         <v>579.5</v>
       </c>
-      <c r="F41" s="6" t="n">
+      <c r="F41" s="7" t="n">
         <v>14.6</v>
       </c>
       <c r="G41" t="n">
@@ -4074,7 +4231,7 @@
       <c r="H41" t="n">
         <v>839.2</v>
       </c>
-      <c r="I41" s="11" t="n">
+      <c r="I41" s="6" t="n">
         <v>1.7</v>
       </c>
       <c r="J41" t="n">
@@ -4083,7 +4240,7 @@
       <c r="K41" t="n">
         <v>1418.6</v>
       </c>
-      <c r="L41" s="11" t="n">
+      <c r="L41" s="6" t="n">
         <v>4.9</v>
       </c>
       <c r="M41" t="n">
@@ -4116,7 +4273,7 @@
       <c r="E42" t="n">
         <v>540.1</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="F42" s="8" t="n">
         <v>9.4</v>
       </c>
       <c r="G42" t="n">
@@ -4125,7 +4282,7 @@
       <c r="H42" t="n">
         <v>845.7</v>
       </c>
-      <c r="I42" s="11" t="n">
+      <c r="I42" s="6" t="n">
         <v>0.9</v>
       </c>
       <c r="J42" t="n">
@@ -4134,7 +4291,7 @@
       <c r="K42" t="n">
         <v>1385.9</v>
       </c>
-      <c r="L42" s="11" t="n">
+      <c r="L42" s="6" t="n">
         <v>3.1</v>
       </c>
       <c r="M42" t="n">
@@ -4167,7 +4324,7 @@
       <c r="E43" t="n">
         <v>518.2</v>
       </c>
-      <c r="F43" s="11" t="n">
+      <c r="F43" s="6" t="n">
         <v>7.6</v>
       </c>
       <c r="G43" t="n">
@@ -4176,7 +4333,7 @@
       <c r="H43" t="n">
         <v>913.3</v>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="I43" s="6" t="n">
         <v>5.8</v>
       </c>
       <c r="J43" t="n">
@@ -4185,7 +4342,7 @@
       <c r="K43" t="n">
         <v>1431.5</v>
       </c>
-      <c r="L43" s="11" t="n">
+      <c r="L43" s="6" t="n">
         <v>6.5</v>
       </c>
       <c r="M43" t="n">
@@ -4218,7 +4375,7 @@
       <c r="E44" t="n">
         <v>546</v>
       </c>
-      <c r="F44" s="12" t="n">
+      <c r="F44" s="8" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="G44" t="n">
@@ -4227,7 +4384,7 @@
       <c r="H44" t="n">
         <v>859.5</v>
       </c>
-      <c r="I44" s="11" t="n">
+      <c r="I44" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="J44" t="n">
@@ -4236,7 +4393,7 @@
       <c r="K44" t="n">
         <v>1405.6</v>
       </c>
-      <c r="L44" s="11" t="n">
+      <c r="L44" s="6" t="n">
         <v>4.2</v>
       </c>
       <c r="M44" t="n">
@@ -4269,7 +4426,7 @@
       <c r="E45" t="n">
         <v>550.6</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="F45" s="8" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="G45" t="n">
@@ -4278,7 +4435,7 @@
       <c r="H45" t="n">
         <v>840.5</v>
       </c>
-      <c r="I45" s="11" t="n">
+      <c r="I45" s="6" t="n">
         <v>1.6</v>
       </c>
       <c r="J45" t="n">
@@ -4287,7 +4444,7 @@
       <c r="K45" t="n">
         <v>1391.1</v>
       </c>
-      <c r="L45" s="11" t="n">
+      <c r="L45" s="6" t="n">
         <v>2.3</v>
       </c>
       <c r="M45" t="n">
@@ -4320,7 +4477,7 @@
       <c r="E46" t="n">
         <v>539</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="F46" s="8" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="G46" t="n">
@@ -4329,7 +4486,7 @@
       <c r="H46" t="n">
         <v>842.7</v>
       </c>
-      <c r="I46" s="11" t="n">
+      <c r="I46" s="6" t="n">
         <v>1.3</v>
       </c>
       <c r="J46" t="n">
@@ -4338,7 +4495,7 @@
       <c r="K46" t="n">
         <v>1381.7</v>
       </c>
-      <c r="L46" s="11" t="n">
+      <c r="L46" s="6" t="n">
         <v>2.8</v>
       </c>
       <c r="M46" t="n">
@@ -4371,7 +4528,7 @@
       <c r="E47" t="n">
         <v>464.7</v>
       </c>
-      <c r="F47" s="11" t="n">
+      <c r="F47" s="6" t="n">
         <v>6.1</v>
       </c>
       <c r="G47" t="n">
@@ -4380,7 +4537,7 @@
       <c r="H47" t="n">
         <v>902.8</v>
       </c>
-      <c r="I47" s="11" t="n">
+      <c r="I47" s="6" t="n">
         <v>5.5</v>
       </c>
       <c r="J47" t="n">
@@ -4389,7 +4546,7 @@
       <c r="K47" t="n">
         <v>1367.4</v>
       </c>
-      <c r="L47" s="11" t="n">
+      <c r="L47" s="6" t="n">
         <v>5.7</v>
       </c>
       <c r="M47" t="n">
@@ -4422,7 +4579,7 @@
       <c r="E48" t="n">
         <v>532</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="F48" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="G48" t="n">
@@ -4431,7 +4588,7 @@
       <c r="H48" t="n">
         <v>840.4</v>
       </c>
-      <c r="I48" s="11" t="n">
+      <c r="I48" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="J48" t="n">
@@ -4440,7 +4597,7 @@
       <c r="K48" t="n">
         <v>1372.4</v>
       </c>
-      <c r="L48" s="11" t="n">
+      <c r="L48" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="M48" t="n">
@@ -4473,7 +4630,7 @@
       <c r="E49" t="n">
         <v>523.9</v>
       </c>
-      <c r="F49" s="11" t="n">
+      <c r="F49" s="6" t="n">
         <v>6.7</v>
       </c>
       <c r="G49" t="n">
@@ -4482,7 +4639,7 @@
       <c r="H49" t="n">
         <v>830.8</v>
       </c>
-      <c r="I49" s="11" t="n">
+      <c r="I49" s="6" t="n">
         <v>2.7</v>
       </c>
       <c r="J49" t="n">
@@ -4491,7 +4648,7 @@
       <c r="K49" t="n">
         <v>1354.7</v>
       </c>
-      <c r="L49" s="11" t="n">
+      <c r="L49" s="6" t="n">
         <v>0.9</v>
       </c>
       <c r="M49" t="n">
@@ -4524,7 +4681,7 @@
       <c r="E50" t="n">
         <v>385.6</v>
       </c>
-      <c r="F50" s="6" t="n">
+      <c r="F50" s="7" t="n">
         <v>15</v>
       </c>
       <c r="G50" t="n">
@@ -4533,7 +4690,7 @@
       <c r="H50" t="n">
         <v>909.2</v>
       </c>
-      <c r="I50" s="11" t="n">
+      <c r="I50" s="6" t="n">
         <v>5.4</v>
       </c>
       <c r="J50" t="n">
@@ -4542,7 +4699,7 @@
       <c r="K50" t="n">
         <v>1294.9</v>
       </c>
-      <c r="L50" s="11" t="n">
+      <c r="L50" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="M50" t="n">
@@ -4575,7 +4732,7 @@
       <c r="E51" t="n">
         <v>396.3</v>
       </c>
-      <c r="F51" s="6" t="n">
+      <c r="F51" s="7" t="n">
         <v>12.4</v>
       </c>
       <c r="G51" t="n">
@@ -4584,7 +4741,7 @@
       <c r="H51" t="n">
         <v>917.3</v>
       </c>
-      <c r="I51" s="11" t="n">
+      <c r="I51" s="6" t="n">
         <v>6.1</v>
       </c>
       <c r="J51" t="n">
@@ -4593,7 +4750,7 @@
       <c r="K51" t="n">
         <v>1313.6</v>
       </c>
-      <c r="L51" s="11" t="n">
+      <c r="L51" s="6" t="n">
         <v>0.6</v>
       </c>
       <c r="M51" t="n">
@@ -4714,7 +4871,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>AI + vision</t>
+          <t>game + disparity</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -4749,17 +4906,17 @@
       <c r="K3" t="n">
         <v>1704</v>
       </c>
-      <c r="L3" s="11" t="n">
+      <c r="L3" s="6" t="n">
         <v>5.8</v>
       </c>
-      <c r="M3" s="11" t="n">
+      <c r="M3" s="6" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AI + vision + DB + net</t>
+          <t>game + disparity + DB + net</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -4794,17 +4951,17 @@
       <c r="K4" t="n">
         <v>2189</v>
       </c>
-      <c r="L4" s="11" t="n">
+      <c r="L4" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="M4" s="11" t="n">
+      <c r="M4" s="6" t="n">
         <v>3.1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>full edge stack, every core</t>
+          <t>six workloads, every core</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -4839,10 +4996,10 @@
       <c r="K5" t="n">
         <v>2561</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="6" t="n">
         <v>0.7</v>
       </c>
     </row>
@@ -4891,10 +5048,10 @@
       <c r="K8" t="n">
         <v>2163</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="6" t="n">
         <v>6.5</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="6" t="n">
         <v>6.5</v>
       </c>
     </row>
@@ -4936,22 +5093,22 @@
       <c r="K9" t="n">
         <v>2878</v>
       </c>
-      <c r="L9" s="11" t="n">
+      <c r="L9" s="6" t="n">
         <v>6.5</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="6" t="n">
         <v>1.4</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>edge mixes: mean 3.6%  worst 5.8%  n=3</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>"pred (QEMU)" uses no silicon counter for the mix: per-application activity from QEMU scaled by each application's solo iteration rate. "pred (PMU)" re-runs the same model on silicon-measured activity, isolating model error from emulator error.</t>
         </is>
@@ -4963,6 +5120,236 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>case</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>workload</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>GB/s</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>ALU Mops/s</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>pred mW</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>meas mW</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>err %</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>iters/s</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>bw_blit_sm</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>blit 4MB — large memcpy (replicate)</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="D2" t="n">
+        <v>290</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2203</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1944</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1325.71</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>bw_blit</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>blit 256MB — large memcpy</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>10.85</v>
+      </c>
+      <c r="D3" t="n">
+        <v>283</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1947</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H3" t="n">
+        <v>20.21</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>bw_reduce</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>reduce 256MB — array reduction</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="D4" t="n">
+        <v>512</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1774</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1797</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>20.36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>bw_spmv</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>spmv 64MB — sparse gather</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="D5" t="n">
+        <v>18</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1305</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1330</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>bw_yuv</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>yuv 1080p — YUV420→RGB565</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="D6" t="n">
+        <v>855</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1393</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1456</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>29.45</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>A pure READ stream at 5.5 GB/s predicts to 1.3%. A 50/50 read+write stream at 11 GB/s over-predicts 12-13%: the model has ONE bandwidth term, so a written byte is charged the same as a read byte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>Predicted from QEMU activity scaled by the silicon iteration rate; no silicon counter in the prediction path. Power MEASURED via BCU busy-window median.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5028,7 +5415,7 @@
           <t>vdd_arm</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="C2" s="8" t="n">
         <v>11.4</v>
       </c>
       <c r="D2" t="n">
@@ -5055,7 +5442,7 @@
           <t>vdd_soc</t>
         </is>
       </c>
-      <c r="C3" s="11" t="n">
+      <c r="C3" s="6" t="n">
         <v>4.1</v>
       </c>
       <c r="D3" t="n">
@@ -5082,7 +5469,7 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="C4" s="11" t="n">
+      <c r="C4" s="6" t="n">
         <v>6.4</v>
       </c>
       <c r="D4" t="n">
@@ -5109,7 +5496,7 @@
           <t>QEMU vs PMU</t>
         </is>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="6" t="n">
         <v>1.75</v>
       </c>
       <c r="D5" t="n">
@@ -5136,7 +5523,7 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="6" t="n">
         <v>3.6</v>
       </c>
       <c r="D6" t="n">
@@ -5163,7 +5550,7 @@
           <t>SUM</t>
         </is>
       </c>
-      <c r="C7" s="11" t="n">
+      <c r="C7" s="6" t="n">
         <v>4.8</v>
       </c>
       <c r="D7" t="n">
@@ -5180,7 +5567,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>rails MEASURED on IMX95LPD5EVK-19 via NXP BCU (busy-window median, see busywin.py); A55 die 40-41 C under load; activity DERIVED from QEMU TCG plugins</t>
         </is>
